--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -183,16 +183,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H68"/>
+  <dimension ref="B2:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (20)</t>
+          <t>NEEDS YOUR DECISION  (9)</t>
         </is>
       </c>
     </row>
@@ -683,17 +683,17 @@
     <row r="8">
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DEC-02</t>
+          <t>DEC-16</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>REVIEW mapping / geography</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he is not on your list of 15.</t>
+          <t>The AU/NZ split is computed as not-NZ versus NZ, so 14 Singapore roles count as AU.</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -703,73 +703,69 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>With him 16 roles 5.230. Without him 15 roles 4.909. Verified REVIEW row 161.</t>
+          <t>PARKED: AU/NZ basis left as is.</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>these are the roles I have for head of tech</t>
-        </is>
-      </c>
+      <c r="H8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>DEC-03</t>
+          <t>DEC-11</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the data reads Technology Manger - Finance Platfoms.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Confirm the three dates: vacancies land 01 Oct 26, offshore transitions done 01 Jan 27, holds stay closed.</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>With him 25 roles 6.777. Without him 24 roles 6.453. Verified REVIEW row 454.</t>
+          <t>PARKED: FY27 dates do not matter right now.</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>i have tech managers as this....what's missing?</t>
+          <t>how do we show where we land for FY27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>DEC-14</t>
+          <t>DEC-17</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of the whole line. Confirm before we share it equally.</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Rob Jadrjevic is counted as a role but priced at zero.</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Others: 297,150 / 298,100 / 291,422 / 417,425 / 343,364. If wrong, the 0.2314 per portfolio share is wrong.</t>
+          <t>PARKED: Rob Jadrjevic left as is.</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr"/>
@@ -778,27 +774,27 @@
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>DEC-15</t>
+          <t>DEC-19</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across portfolios or only filled ones are.</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Six Ring fenced placeholder rows: keep, cost, or exclude.</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Filled 3 = 0.694. Vacant 4 = 0.971. Sharing all 7 gives 0.1665 each; filled only gives 0.0694 each.</t>
+          <t>Rows 458 onwards.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr"/>
@@ -807,370 +803,336 @@
     <row r="12">
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>DEC-04</t>
+          <t>DEC-09</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to their own division.</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>The Left to fund 1.48 line: real, or covered by something.</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>5.10 actual against a 3.00 allowance. Equal share is 0.510 per portfolio. Note they sit outside the 528 role mapping.</t>
+          <t>Sits under the mislabelled EGI line.</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>We also need to price in the GMs, have we done that?</t>
-        </is>
-      </c>
+      <c r="H12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>DEC-07</t>
+          <t>DEC-20</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>0.805 is the 1.14 funding model. 0.838 is actual less the uplift programme.</t>
-        </is>
-      </c>
+          <t>A 0.165 platform overhead is priced onto the Data NZ platform. Confirm or reverse.</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>We need a single lense and no confusion.</t>
-        </is>
-      </c>
+      <c r="H13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>DEC-10</t>
+          <t>DEC-12</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>2.13 COE SA&amp;D</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr"/>
+          <t>Restore the Paused roles - cost if released line that was on your old 1.12, or leave it out.</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>It read 0 at consolidation so it was not carried.</t>
+        </is>
+      </c>
       <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="15" t="inlineStr">
-        <is>
-          <t>it might be that we do it in the 2.x tabs or actually we do it in the data config tab or it's its own tab on itself</t>
-        </is>
-      </c>
+      <c r="H14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>DEC-16</t>
+          <t>DEC-13</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / geography</t>
+          <t>Value adds</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>The AU/NZ split is computed as not-NZ versus NZ, so 14 Singapore roles count as AU.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Affects every AU/NZ line on the 1.x tabs.</t>
-        </is>
-      </c>
+          <t>Which additions you want: in year phasing, saved scenarios, offshore transition assumptions, assumptions register, actioned vs planned, contractor roll off.</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Keen to see what you said is worth adding.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>DEC-05</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Overheads / programmes</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>Changes how much overhead sits on Retail and Commercial Fuels.</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>EGI does not use overheads. if they're egi they're egi, it's simple.</t>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>AGREED, NOT BUILT YET  (36)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>DEC-06</t>
+          <t>BLD-01</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD Group Functions with the other four, or leave him.</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it in the funding block.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>REVIEW row 104, contractor, 299,700, Division Ampol Retail &amp; Z.</t>
+          <t>Verified absent: 1.3 B34 only says Platform: EGI Data - removed, no roles. The EGI funding line reads 0.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr"/>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>I don;t know why ampol retail has egi tdd??</t>
+          <t>there needs to be a whole new platform and squad that says egi ent data on 1.3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>DEC-08</t>
+          <t>BLD-02</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Blank stops accidents and still lets you turn it off in one click.</t>
+          <t>Verified: 1.1 J18 = 1.221357614, misses 0.2997.</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>how do we protect the workbook? any suggestions?</t>
-        </is>
-      </c>
+      <c r="H18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>DEC-11</t>
+          <t>BLD-03</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Confirm the three dates: vacancies land 01 Oct 26, offshore transitions done 01 Jan 27, holds stay closed.</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such line.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Under those defaults FY27 lands at 102.01 against a 106.80 run rate.</t>
+          <t>Verified: 1.02484851 appears nowhere on 3.4.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>how do we show where we land for FY27</t>
-        </is>
-      </c>
+      <c r="H19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>DEC-17</t>
+          <t>BLD-04</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Rob Jadrjevic is counted as a role but priced at zero.</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds every overhead role, nothing recharged.</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>REVIEW row 190, Engineer BE, Customer / EGI Customer.</t>
+          <t>Platform: Delivery Manager, Technology Manager. Portfolio: Head of Tech, Business Partner, Domain Architect, GMs.</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="15" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>TDD pays for every single overhead role, nothing is recharged</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>DEC-18</t>
+          <t>BLD-05</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actual cost.</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Makes the FTE total and the cost total tell different stories.</t>
+          <t>BP 2.3135 / 10 = 0.2314 each. DA 1.6647 / 10 = 0.1665 each. Up from the 0.22 and 0.14 allowances.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>domain architects and business partners needs to be equally shared across portfolios</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>DEC-19</t>
+          <t>BLD-06</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Six Ring fenced placeholder rows: keep, cost, or exclude.</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Rows 458 onwards.</t>
+          <t>COE spend falls 0.378, portfolios pick up 0.378. People stay listed on the COE tabs.</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="15" t="inlineStr"/>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>what is the impact on the coes tabs</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>DEC-09</t>
+          <t>BLD-07</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>The Left to fund 1.48 line: real, or covered by something.</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make it consistent.</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Sits under the mislabelled EGI line.</t>
+          <t>Verified: 3.1 I18 = 6.176556022 is the gross figure.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr"/>
@@ -1179,107 +1141,141 @@
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>DEC-20</t>
+          <t>BLD-08</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>A 0.165 platform overhead is priced onto the Data NZ platform. Confirm or reverse.</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr"/>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype support percentages, plus overheads, against the lights on budget and against what can be recharged.</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Uses your Other funding block shape: budget line, amount that can be allocated to people, total applied, left to fund.</t>
+        </is>
+      </c>
       <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>in the yellow, you'll see it there, that's what i expect</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>DEC-12</t>
+          <t>BLD-09</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>2.13 COE SA&amp;D</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Restore the Paused roles - cost if released line that was on your old 1.12, or leave it out.</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>It read 0 at consolidation so it was not carried.</t>
-        </is>
-      </c>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>it's not to projects it's a rechargeable amount</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>DEC-13</t>
+          <t>BLD-10</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Value adds</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Which additions you want: in year phasing, saved scenarios, offshore transition assumptions, assumptions register, actioned vs planned, contractor roll off.</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr"/>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacancy keeps its ID when filled.</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent: no Role ID anywhere. This is what makes a mapping refresh safe.</t>
+        </is>
+      </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Keen to see what you said is worth adding.</t>
+          <t>We defo need mapping to roleid, but note that some roles have vacant ties</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>AGREED, NOT BUILT YET  (22)</t>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>BLD-11</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Single lens everywhere so no number needs interpreting.</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-01</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it in the funding block.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1287,32 +1283,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent: 1.3 B34 only says Platform: EGI Data - removed, no roles. The EGI funding line reads 0.</t>
-        </is>
-      </c>
+      <c r="F28" s="14" t="inlineStr"/>
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>there needs to be a whole new platform and squad that says egi ent data on 1.3</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-02</t>
+          <t>BLD-16</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1322,26 +1314,30 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Verified: 1.1 J18 = 1.221357614, misses 0.2997.</t>
+          <t>Verified: no protection anywhere today.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>how do we protect the workbook?</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-03</t>
+          <t>BLD-17</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such line.</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every control stays 0 and every number is identical.</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1349,28 +1345,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 1.02484851 appears nowhere on 3.4.</t>
-        </is>
-      </c>
+      <c r="F30" s="14" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="15" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>updating the review tab right now siginificantly breaks the model</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-04</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds every overhead role, nothing recharged.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1378,32 +1374,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Platform: Delivery Manager, Technology Manager. Portfolio: Head of Tech, Business Partner, Domain Architect, GMs.</t>
-        </is>
-      </c>
+      <c r="F31" s="8" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>TDD pays for every single overhead role, nothing is recharged</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-05</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actual cost.</t>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1411,218 +1403,190 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>BP 2.3135 / 10 = 0.2314 each. DA 1.6647 / 10 = 0.1665 each. Up from the 0.22 and 0.14 allowances.</t>
-        </is>
-      </c>
+      <c r="F32" s="14" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>domain architects and business partners needs to be equally shared across portfolios</t>
+          <t>what have you changed that i didn't ask for?</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-06</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>COE spend falls 0.378, portfolios pick up 0.378. People stay listed on the COE tabs.</t>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>what is the impact on the coes tabs</t>
-        </is>
-      </c>
+      <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-07</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make it consistent.</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 3.1 I18 = 6.176556022 is the gross figure.</t>
-        </is>
-      </c>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr"/>
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-08</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype support percentages, plus overheads, against the lights on budget and against what can be recharged.</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Uses your Other funding block shape: budget line, amount that can be allocated to people, total applied, left to fund.</t>
-        </is>
-      </c>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr"/>
       <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>in the yellow, you'll see it there, that's what i expect</t>
-        </is>
-      </c>
+      <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-09</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr"/>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Mechanically right, reads odd.</t>
+        </is>
+      </c>
       <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="15" t="inlineStr">
-        <is>
-          <t>it's not to projects it's a rechargeable amount</t>
-        </is>
-      </c>
+      <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-10</t>
+          <t>BLD-18</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.7 and 2.8</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacancy keeps its ID when filled.</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Verified absent: no Role ID anywhere. This is what makes a mapping refresh safe.</t>
+          <t>2 on Infrastructure, 2 on Energy Solutions &amp; B2B.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>We defo need mapping to roleid, but note that some roles have vacant ties</t>
-        </is>
-      </c>
+      <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-11</t>
+          <t>BLD-19</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
-        </is>
-      </c>
+      <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-R-02</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he is not on your list of 15.</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -1630,28 +1594,32 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>RULED: Ed Tacey OFF the Heads line, reverts to his 30/07 coding. HoT = 15 roles, 4.909.</t>
+        </is>
+      </c>
       <c r="G39" s="9" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>these are the roles I have for head of tech</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-16</t>
+          <t>BLD-R-03</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the data reads Technology Manger - Finance Platfoms.</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1661,30 +1629,30 @@
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Verified: no protection anywhere today.</t>
+          <t>RULED: Shane Ker stays IN Technology Manager. Line stays 25 roles, 6.777.</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>how do we protect the workbook?</t>
+          <t>i have tech managers as this....what's missing?</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-17</t>
+          <t>BLD-R-14</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every control stays 0 and every number is identical.</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of the whole line. Confirm before we share it equally.</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1692,28 +1660,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>RULED: Neil Reilly costed in at 666,088.</t>
+        </is>
+      </c>
       <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>updating the review tab right now siginificantly breaks the model</t>
-        </is>
-      </c>
+      <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-R-15</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across portfolios or only filled ones are.</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1721,28 +1689,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr"/>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>RULED: vacant roles are shared when set to Hire; Hold roles are never priced.</t>
+        </is>
+      </c>
       <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="15" t="inlineStr">
-        <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
-        </is>
-      </c>
+      <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-R-04</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to their own division.</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1750,312 +1718,372 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>RULED: GMs priced equally across the 10 portfolios, 0.510 each.</t>
+        </is>
+      </c>
       <c r="G43" s="9" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>We also need to price in the GMs, have we done that?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-R-07</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+          <t>RULED: TDD Cyber shows the accurate number, the actuals basis, one lens everywhere.</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="15" t="inlineStr"/>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>We need a single lense and no confusion.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-R-10</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr"/>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>RULED: lights on is its own tab.</t>
+        </is>
+      </c>
       <c r="G45" s="9" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>it might be that we do it in the 2.x tabs or actually we do it in the data config tab or it's its own tab on itself</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-R-05</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr"/>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>RULED: AmPOS and CTRM carry no overhead, same as EGI.</t>
+        </is>
+      </c>
       <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="15" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>EGI does not use overheads. if they're egi they're egi, it's simple.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-R-06</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD Group Functions with the other four, or leave him.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Mechanically right, reads odd.</t>
+          <t>RULED: Viren Khatri retagged into TDD Group Functions with the other four EGI TDD roles.</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr"/>
-      <c r="H47" s="10" t="inlineStr"/>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>I don;t know why ampol retail has egi tdd??</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>BLD-18</t>
+          <t>BLD-R-08</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2.7 and 2.8</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>Blank password or a real one.</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>2 on Infrastructure, 2 on Energy Solutions &amp; B2B.</t>
+          <t>RULED: password Tdd123, and the role mapping tab locked down.</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr"/>
-      <c r="H48" s="15" t="inlineStr"/>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>how do we protect the workbook? any suggestions?</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>BLD-19</t>
+          <t>BLD-R-18</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
-        </is>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr"/>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>RULED: the seven part time people are scaled by their FTE.</t>
+        </is>
+      </c>
       <c r="G49" s="9" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (16)</t>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>BLD-23</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Lights On tab</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Over/Under), flat list like 0.2, TDD Cyber inline, archetype cost shown for comparison. Toggle A: a cream percentage per portfolio, 0 to 100, for how much overhead is charged to lights on. Toggle B: overhead broken out into BP, DA and GM shares (fixed equal splits) plus Other overheads with a percentage lever, his example 50 percent. Awaiting his example layout before final shape.</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>His construction confirmed at 62.61 vs 50.50. This is the centrepiece of the build.</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>I need a toggle... percentage of overhead charged to TDD lights on... 0 to 100 percent</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E51" s="19" t="inlineStr"/>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the Delivery Manager line per his list. Line becomes 12 roles, 3.333.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
-      <c r="H51" s="10" t="inlineStr"/>
+          <t>Both 275,810, currently coded Squad in COE BP&amp;T.</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr"/>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>should be these if i stand corrected</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>BLD-25</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="inlineStr"/>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only those.</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
-      <c r="H52" s="15" t="inlineStr"/>
+          <t>Awaiting the file.</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr"/>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>i think it's just on the levers</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>DNE-03</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>REVIEW mapping</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
-        </is>
-      </c>
-      <c r="E53" s="19" t="inlineStr"/>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>528 roles, 394 filled, 134 vacant</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
-      <c r="H53" s="10" t="inlineStr"/>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (16)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr"/>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="inlineStr"/>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -2065,197 +2093,197 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="inlineStr"/>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>528 roles, 394 filled, 134 vacant</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="inlineStr"/>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G57" s="22" t="inlineStr"/>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
-        </is>
-      </c>
-      <c r="E58" s="18" t="inlineStr"/>
+          <t>Programme Management as a Customer only overhead line</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
-        </is>
-      </c>
-      <c r="E59" s="19" t="inlineStr"/>
+          <t>Ed Tacey follows the data onto the Heads line</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="inlineStr"/>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
-        </is>
-      </c>
-      <c r="E61" s="19" t="inlineStr"/>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Verified: all 43 sheets unprotected</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
-        </is>
-      </c>
-      <c r="E62" s="18" t="inlineStr"/>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr"/>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
@@ -2265,22 +2293,22 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="inlineStr"/>
+          <t>No sheet or workbook protection anywhere</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>Verified: all 43 sheets unprotected</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -2290,60 +2318,135 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
-        </is>
-      </c>
-      <c r="E65" s="19" t="inlineStr"/>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
+          <t>DNE-13</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr"/>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
+      <c r="H66" s="15" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>DNE-14</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>The word wave appears nowhere</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
+      <c r="H67" s="10" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>DNE-15</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr"/>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
+      <c r="H68" s="15" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
           <t>DNE-16</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr"/>
-      <c r="F66" s="14" t="inlineStr">
+      <c r="E69" s="18" t="inlineStr"/>
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>494,819 charged</t>
         </is>
       </c>
-      <c r="G66" s="23" t="inlineStr"/>
-      <c r="H66" s="15" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>20 decisions, 22 to build, 16 done. Nothing has been built since the file you have.</t>
+      <c r="G69" s="23" t="inlineStr"/>
+      <c r="H69" s="10" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>9 decisions, 36 to build, 16 done. Nothing has been built since the file you have.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B50:H50"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B53:H53"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B16:H16"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -915,24 +915,24 @@
     <row r="16">
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>AGREED, NOT BUILT YET  (36)</t>
+          <t>AGREED, NOT BUILT YET  (10)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>BLD-01</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it in the funding block.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -940,32 +940,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent: 1.3 B34 only says Platform: EGI Data - removed, no roles. The EGI funding line reads 0.</t>
-        </is>
-      </c>
+      <c r="F17" s="8" t="inlineStr"/>
       <c r="G17" s="9" t="inlineStr"/>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>there needs to be a whole new platform and squad that says egi ent data on 1.3</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>BLD-02</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -973,28 +969,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 1.1 J18 = 1.221357614, misses 0.2997.</t>
-        </is>
-      </c>
+      <c r="F18" s="14" t="inlineStr"/>
       <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="15" t="inlineStr"/>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>BLD-03</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such line.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1002,28 +998,28 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 1.02484851 appears nowhere on 3.4.</t>
-        </is>
-      </c>
+      <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>BLD-04</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds every overhead role, nothing recharged.</t>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -1031,1025 +1027,853 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Platform: Delivery Manager, Technology Manager. Portfolio: Head of Tech, Business Partner, Domain Architect, GMs.</t>
-        </is>
-      </c>
+      <c r="F20" s="14" t="inlineStr"/>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>TDD pays for every single overhead role, nothing is recharged</t>
+          <t>what have you changed that i didn't ask for?</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>BLD-05</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actual cost.</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>BP 2.3135 / 10 = 0.2314 each. DA 1.6647 / 10 = 0.1665 each. Up from the 0.22 and 0.14 allowances.</t>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>domain architects and business partners needs to be equally shared across portfolios</t>
-        </is>
-      </c>
+      <c r="H21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>BLD-06</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>COE spend falls 0.378, portfolios pick up 0.378. People stay listed on the COE tabs.</t>
-        </is>
-      </c>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr"/>
       <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="15" t="inlineStr">
-        <is>
-          <t>what is the impact on the coes tabs</t>
-        </is>
-      </c>
+      <c r="H22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>BLD-07</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make it consistent.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 3.1 I18 = 6.176556022 is the gross figure.</t>
-        </is>
-      </c>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>BLD-08</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype support percentages, plus overheads, against the lights on budget and against what can be recharged.</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Uses your Other funding block shape: budget line, amount that can be allocated to people, total applied, left to fund.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>in the yellow, you'll see it there, that's what i expect</t>
-        </is>
-      </c>
+      <c r="H24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>BLD-09</t>
+          <t>BLD-18</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>2.7 and 2.8</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr"/>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>2 on Infrastructure, 2 on Energy Solutions &amp; B2B.</t>
+        </is>
+      </c>
       <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>it's not to projects it's a rechargeable amount</t>
-        </is>
-      </c>
+      <c r="H25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-10</t>
+          <t>BLD-19</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacancy keeps its ID when filled.</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent: no Role ID anywhere. This is what makes a mapping refresh safe.</t>
-        </is>
-      </c>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr"/>
       <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>We defo need mapping to roleid, but note that some roles have vacant ties</t>
-        </is>
-      </c>
+      <c r="H26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (42)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="15" t="inlineStr">
-        <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
-        </is>
-      </c>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-16</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Verified: no protection anywhere today.</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>how do we protect the workbook?</t>
-        </is>
-      </c>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-17</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every control stays 0 and every number is identical.</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr"/>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>updating the review tab right now siginificantly breaks the model</t>
-        </is>
-      </c>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>528 roles, 394 filled, 134 vacant</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
-        </is>
-      </c>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr"/>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="15" t="inlineStr">
-        <is>
-          <t>what have you changed that i didn't ask for?</t>
-        </is>
-      </c>
+          <t>Programme Management as a Customer only overhead line</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr"/>
+      <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+          <t>Ed Tacey follows the data onto the Heads line</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="9" t="inlineStr"/>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-18</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2.7 and 2.8</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2 on Infrastructure, 2 on Energy Solutions &amp; B2B.</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-19</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr"/>
-      <c r="G38" s="9" t="inlineStr"/>
+          <t>No sheet or workbook protection anywhere</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Verified: all 43 sheets unprotected</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-R-02</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he is not on your list of 15.</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>RULED: Ed Tacey OFF the Heads line, reverts to his 30/07 coding. HoT = 15 roles, 4.909.</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>these are the roles I have for head of tech</t>
-        </is>
-      </c>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-R-03</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the data reads Technology Manger - Finance Platfoms.</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>RULED: Shane Ker stays IN Technology Manager. Line stays 25 roles, 6.777.</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="15" t="inlineStr">
-        <is>
-          <t>i have tech managers as this....what's missing?</t>
-        </is>
-      </c>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr"/>
+      <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-R-14</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of the whole line. Confirm before we share it equally.</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>The word wave appears nowhere</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>RULED: Neil Reilly costed in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-R-15</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across portfolios or only filled ones are.</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>RULED: vacant roles are shared when set to Hire; Hold roles are never priced.</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BLD-R-04</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to their own division.</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Cyber uplift percentage column feeding 1.14</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>RULED: GMs priced equally across the 10 portfolios, 0.510 each.</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>We also need to price in the GMs, have we done that?</t>
-        </is>
-      </c>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BLD-R-07</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>RULED: TDD Cyber shows the accurate number, the actuals basis, one lens everywhere.</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="15" t="inlineStr">
-        <is>
-          <t>We need a single lense and no confusion.</t>
-        </is>
-      </c>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr"/>
+      <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>BLD-R-10</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>RULED: lights on is its own tab.</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>it might be that we do it in the 2.x tabs or actually we do it in the data config tab or it's its own tab on itself</t>
-        </is>
-      </c>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>BLD-R-05</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>RULED: AmPOS and CTRM carry no overhead, same as EGI.</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="15" t="inlineStr">
-        <is>
-          <t>EGI does not use overheads. if they're egi they're egi, it's simple.</t>
-        </is>
-      </c>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>BLD-R-06</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD Group Functions with the other four, or leave him.</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>RULED: Viren Khatri retagged into TDD Group Functions with the other four EGI TDD roles.</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr"/>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>I don;t know why ampol retail has egi tdd??</t>
-        </is>
-      </c>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr"/>
+      <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>BLD-R-08</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>RULED: password Tdd123, and the role mapping tab locked down.</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr"/>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>how do we protect the workbook? any suggestions?</t>
-        </is>
-      </c>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
+      <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>BLD-R-18</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>RULED: the seven part time people are scaled by their FTE.</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Over/Under), flat list like 0.2, TDD Cyber inline, archetype cost shown for comparison. Toggle A: a cream percentage per portfolio, 0 to 100, for how much overhead is charged to lights on. Toggle B: overhead broken out into BP, DA and GM shares (fixed equal splits) plus Other overheads with a percentage lever, his example 50 percent. Awaiting his example layout before final shape.</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>His construction confirmed at 62.61 vs 50.50. This is the centrepiece of the build.</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="15" t="inlineStr">
-        <is>
-          <t>I need a toggle... percentage of overhead charged to TDD lights on... 0 to 100 percent</t>
-        </is>
-      </c>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the Delivery Manager line per his list. Line becomes 12 roles, 3.333.</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Both 275,810, currently coded Squad in COE BP&amp;T.</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>should be these if i stand corrected</t>
-        </is>
-      </c>
+          <t>DONE: every sheet locked, only levers, uplift cells and cream inputs open, REVIEW fully locked, structure locked, password Tdd123; gate K 6/6.</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
+      <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only those.</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Awaiting the file.</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr"/>
-      <c r="H52" s="15" t="inlineStr">
-        <is>
-          <t>i think it's just on the levers</t>
-        </is>
-      </c>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
+      <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (16)</t>
-        </is>
-      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>DNE-26</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Overheads / Head of Tech</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
+      <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
         </is>
       </c>
       <c r="G54" s="22" t="inlineStr"/>
@@ -2058,23 +1882,23 @@
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
+          <t>DONE: Neil Reilly in at 666,088.</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr"/>
@@ -2083,23 +1907,23 @@
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>528 roles, 394 filled, 134 vacant</t>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
         </is>
       </c>
       <c r="G56" s="22" t="inlineStr"/>
@@ -2108,23 +1932,23 @@
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr"/>
@@ -2133,23 +1957,23 @@
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
         </is>
       </c>
       <c r="G58" s="22" t="inlineStr"/>
@@ -2158,23 +1982,23 @@
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr"/>
@@ -2183,23 +2007,23 @@
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr"/>
@@ -2208,23 +2032,23 @@
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr"/>
@@ -2233,23 +2057,23 @@
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>DONE: password Tdd123, role mapping fully locked; gate K.</t>
         </is>
       </c>
       <c r="G62" s="22" t="inlineStr"/>
@@ -2258,23 +2082,23 @@
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr"/>
@@ -2283,23 +2107,23 @@
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>Verified: all 43 sheets unprotected</t>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50.</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr"/>
@@ -2308,23 +2132,23 @@
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr"/>
@@ -2333,23 +2157,23 @@
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr"/>
@@ -2358,23 +2182,23 @@
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr"/>
@@ -2383,23 +2207,23 @@
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr"/>
@@ -2408,23 +2232,23 @@
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr"/>
@@ -2433,14 +2257,14 @@
     <row r="71">
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>9 decisions, 36 to build, 16 done. Nothing has been built since the file you have.</t>
+          <t>9 decisions, 10 to build, 42 done. Nothing has been built since the file you have.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B27:H27"/>
     <mergeCell ref="B71:H71"/>
-    <mergeCell ref="B53:H53"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B3:H3"/>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H71"/>
+  <dimension ref="B2:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Rows 458 onwards.</t>
+          <t>Your 05/08 mapping carries four rows named ring fenced. They price as vacancies today, on their levers.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr"/>
@@ -915,7 +915,7 @@
     <row r="16">
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>AGREED, NOT BUILT YET  (10)</t>
+          <t>AGREED, NOT BUILT YET  (8)</t>
         </is>
       </c>
     </row>
@@ -1144,86 +1144,82 @@
       <c r="H24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>BLD-18</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>2.7 and 2.8</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>2 on Infrastructure, 2 on Energy Solutions &amp; B2B.</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (50)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-19</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr"/>
-      <c r="G26" s="9" t="inlineStr"/>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr"/>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr"/>
       <c r="H26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (42)</t>
-        </is>
-      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>DNE-02</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>2.x lever tabs</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr"/>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr"/>
@@ -1232,23 +1228,23 @@
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr"/>
@@ -1257,23 +1253,23 @@
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr"/>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>528 roles, 394 filled, 134 vacant</t>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr"/>
@@ -1282,23 +1278,23 @@
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr"/>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified row 161. Now under review, see DEC-02</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr"/>
@@ -1307,23 +1303,23 @@
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr"/>
@@ -1332,23 +1328,23 @@
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr"/>
@@ -1357,17 +1353,17 @@
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr"/>
@@ -1382,23 +1378,23 @@
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>1.11, 1.12, 1.13 deleted</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr"/>
@@ -1407,23 +1403,23 @@
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr"/>
@@ -1432,23 +1428,23 @@
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
+          <t>72 validations, 54 white rows</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr"/>
@@ -1457,7 +1453,7 @@
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
@@ -1467,13 +1463,13 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Verified: all 43 sheets unprotected</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr"/>
@@ -1482,7 +1478,7 @@
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1492,13 +1488,13 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
+          <t>Verified twice across all 43 sheets</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr"/>
@@ -1507,7 +1503,7 @@
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -1517,13 +1513,13 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr"/>
@@ -1532,23 +1528,23 @@
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
+          <t>494,819 charged</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr"/>
@@ -1557,23 +1553,23 @@
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr"/>
@@ -1582,23 +1578,23 @@
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr"/>
@@ -1607,23 +1603,23 @@
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
         </is>
       </c>
       <c r="G44" s="22" t="inlineStr"/>
@@ -1632,23 +1628,23 @@
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr"/>
@@ -1657,23 +1653,23 @@
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
         </is>
       </c>
       <c r="G46" s="22" t="inlineStr"/>
@@ -1682,23 +1678,23 @@
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr"/>
@@ -1707,23 +1703,23 @@
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr"/>
@@ -1732,23 +1728,23 @@
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr"/>
@@ -1757,23 +1753,23 @@
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
         </is>
       </c>
       <c r="G50" s="22" t="inlineStr"/>
@@ -1782,23 +1778,23 @@
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE: every sheet locked, only levers, uplift cells and cream inputs open, REVIEW fully locked, structure locked, password Tdd123; gate K 6/6.</t>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr"/>
@@ -1807,23 +1803,23 @@
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
         </is>
       </c>
       <c r="G52" s="22" t="inlineStr"/>
@@ -1832,23 +1828,23 @@
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+          <t>DONE: Neil Reilly in at 666,088.</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr"/>
@@ -1857,23 +1853,23 @@
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
         </is>
       </c>
       <c r="G54" s="22" t="inlineStr"/>
@@ -1882,23 +1878,23 @@
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr"/>
@@ -1907,23 +1903,23 @@
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
         </is>
       </c>
       <c r="G56" s="22" t="inlineStr"/>
@@ -1932,23 +1928,23 @@
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr"/>
@@ -1957,23 +1953,23 @@
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
         </is>
       </c>
       <c r="G58" s="22" t="inlineStr"/>
@@ -1982,23 +1978,23 @@
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr"/>
@@ -2007,23 +2003,23 @@
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr"/>
@@ -2032,23 +2028,23 @@
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr"/>
@@ -2057,23 +2053,23 @@
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123, role mapping fully locked; gate K.</t>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50.</t>
         </is>
       </c>
       <c r="G62" s="22" t="inlineStr"/>
@@ -2082,23 +2078,23 @@
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr"/>
@@ -2107,23 +2103,23 @@
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50.</t>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr"/>
@@ -2132,23 +2128,23 @@
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr"/>
@@ -2157,23 +2153,23 @@
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr"/>
@@ -2182,23 +2178,23 @@
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr"/>
@@ -2207,23 +2203,23 @@
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr"/>
@@ -2232,45 +2228,195 @@
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>DNE-45</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>REVIEW mapping</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr"/>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
+      <c r="H70" s="15" t="inlineStr"/>
+    </row>
     <row r="71">
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>9 decisions, 10 to build, 42 done. Nothing has been built since the file you have.</t>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>DNE-46</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
+      <c r="H71" s="10" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>DNE-47</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Overheads / TDD Cyber</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr"/>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
+      <c r="H72" s="15" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>DNE-48</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Language / Enterprise Data</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
+      <c r="H73" s="10" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>DNE-49</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>3.5 TDD Lights On</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr"/>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
+      <c r="H74" s="15" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>DNE-50</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>3.6 TDD Lights On AU NZ</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
+      <c r="H75" s="10" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>9 decisions, 8 to build, 50 done. Nothing has been built since the file you have.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B77:H77"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -2403,7 +2403,7 @@
     <row r="77">
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>9 decisions, 8 to build, 50 done. Nothing has been built since the file you have.</t>
+          <t>9 decisions, 8 to build, 50 done.</t>
         </is>
       </c>
     </row>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H77"/>
+  <dimension ref="B2:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1146,7 @@
     <row r="25">
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (50)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (54)</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50.</t>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
         </is>
       </c>
       <c r="G62" s="22" t="inlineStr"/>
@@ -2400,23 +2400,123 @@
       <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>DNE-51</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>3.5 TDD Lights On</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr"/>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
+      <c r="H76" s="15" t="inlineStr"/>
+    </row>
     <row r="77">
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>9 decisions, 8 to build, 50 done.</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>DNE-52</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>COE pair rows</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Each COE line carries its own people, not a proportional share.</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
+      <c r="H77" s="10" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>DNE-53</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>EGI</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>EGI is EGI - the whole family in one place.</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr"/>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>DNE-54</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW mapping</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>The tab must read exactly as his file does, visibility included.</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr"/>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
+      <c r="H79" s="10" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>9 decisions, 8 to build, 54 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B77:H77"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B81:H81"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H81"/>
+  <dimension ref="B2:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1146,7 @@
     <row r="25">
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (54)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (62)</t>
         </is>
       </c>
     </row>
@@ -2500,10 +2500,210 @@
       <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>DNE-55</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>3.5 TDD Lights On</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Show how the columns add to the total people cost.</t>
+        </is>
+      </c>
+      <c r="E80" s="19" t="inlineStr"/>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
+      <c r="H80" s="15" t="inlineStr"/>
+    </row>
     <row r="81">
-      <c r="B81" s="24" t="inlineStr">
-        <is>
-          <t>9 decisions, 8 to build, 54 done.</t>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>DNE-56</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>EGI</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr"/>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
+      <c r="H81" s="10" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>DNE-57</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Overheads</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr"/>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
+      <c r="H82" s="15" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>DNE-58</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Get rid of the control checks.</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
+      <c r="H83" s="10" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>DNE-59</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>0.2 Data Config</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr"/>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
+      <c r="H84" s="15" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>DNE-60</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>One sign convention for over budget.</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
+      <c r="H85" s="10" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>DNE-61</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>1.x tabs</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr"/>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
+      <c r="H86" s="15" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>DNE-62</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>3.6 TDD Lights On AU NZ</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Answer whether the overspend is AU or NZ.</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
+      <c r="H87" s="10" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>9 decisions, 8 to build, 62 done.</t>
         </is>
       </c>
     </row>
@@ -2513,10 +2713,10 @@
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B89:H89"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H89"/>
+  <dimension ref="B2:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (9)</t>
+          <t>NEEDS YOUR DECISION  (12)</t>
         </is>
       </c>
     </row>
@@ -913,26 +913,52 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>AGREED, NOT BUILT YET  (8)</t>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>DEC-21</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Plain English forever - every question, label and note. Jargon-phrased questions get rethought before being asked.</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Ruled 06/08.</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>I need plain english forever. save to memory.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>BLD-11</t>
+          <t>DEC-22</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Cyber split</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
+          <t>2.11 splits into Cyber COE (Cyber GRC, Cyber Risk, Cyber Sec Ops, Cyber Strat &amp; Tech; 1.5) and Service Ops COE (Service Op &amp; Assurance; 0.5). Membership from the Squad column, raw block untouched. GM base goes to 17.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -940,28 +966,32 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>AU/NZ split of the two budgets still to come.</t>
+        </is>
+      </c>
       <c r="G17" s="9" t="inlineStr"/>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
+          <t>cyber risk is in cyber. splitting it like that is fine.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>DEC-23</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Build order</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Support percentages and budget tables move to the 2.x tabs first (1.x become formula views; archetype tables stay), then the cyber split, then FY26.</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -969,47 +999,29 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Agreed 06/08.</t>
+        </is>
+      </c>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I agree on the process of everything being done.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>BLD-20</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>COE tabs</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>AGREED, NOT BUILT YET  (8)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -1019,7 +1031,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -1031,103 +1043,111 @@
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr"/>
       <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="15" t="inlineStr"/>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -1137,148 +1157,152 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Mechanically right, reads odd.</t>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (62)</t>
-        </is>
-      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>BLD-13</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>0.0 Cockpit</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr"/>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G26" s="22" t="inlineStr"/>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr"/>
+      <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr"/>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr"/>
+          <t>Mechanically right, reads odd.</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>DNE-03</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>REVIEW mapping</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr"/>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="inlineStr"/>
-      <c r="H28" s="15" t="inlineStr"/>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (62)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr"/>
       <c r="H29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr"/>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1288,32 +1312,32 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr"/>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr"/>
@@ -1322,163 +1346,163 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr"/>
+      <c r="G32" s="23" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1488,22 +1512,22 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -1513,1022 +1537,1022 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -2538,185 +2562,260 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
+      <c r="H87" s="10" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>DNE-60</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Whole model</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>One sign convention for over budget.</t>
+        </is>
+      </c>
+      <c r="E88" s="19" t="inlineStr"/>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
+      <c r="H88" s="15" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>DNE-61</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>1.x tabs</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
+      <c r="H89" s="10" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>DNE-62</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>3.6 TDD Lights On AU NZ</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Answer whether the overspend is AU or NZ.</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr"/>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
           <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr"/>
-      <c r="H87" s="10" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="24" t="inlineStr">
-        <is>
-          <t>9 decisions, 8 to build, 62 done.</t>
+      <c r="G90" s="23" t="inlineStr"/>
+      <c r="H90" s="15" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>12 decisions, 8 to build, 62 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B92:H92"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G91" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -968,7 +968,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>AU/NZ split of the two budgets still to come.</t>
+          <t>AU/NZ split ruled 06/08: Cyber 1.0 AU / 0.5 NZ; Service Ops 0.5 AU / 0 NZ.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr"/>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H92"/>
+  <dimension ref="B2:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (12)</t>
+          <t>NEEDS YOUR DECISION  (13)</t>
         </is>
       </c>
     </row>
@@ -1012,45 +1012,49 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>DEC-24</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>EGI / GM / offshore rulings</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Platform beginning EGI = funded outside (catches EGI Customer x3). GM pot divides by 11, the 16-line basis is dead. The nine offshore Enterprise Data delivery roles carry the Offshore lever with cost unchanged (WiPro-style exemption).</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Ruled 06/08 on the audit questions.</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>they should be egi funded. GM pot is 11. ent data should be offshore lever sure, but the cost shouldn't change with the dials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1060,7 +1064,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1072,24 +1076,24 @@
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -1101,24 +1105,24 @@
       <c r="G22" s="9" t="inlineStr"/>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1130,53 +1134,53 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr"/>
       <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
@@ -1184,24 +1188,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
@@ -1216,17 +1224,17 @@
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -1234,210 +1242,210 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>BLD-22</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>2.9 Commercial Fuels</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Mechanically right, reads odd.</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (62)</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G29" s="22" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr"/>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr"/>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G31" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
@@ -1446,13 +1454,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G36" s="23" t="inlineStr"/>
+      <c r="G36" s="22" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1462,7 +1470,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
@@ -1471,63 +1479,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr"/>
+      <c r="G37" s="23" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -1537,22 +1545,22 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1562,22 +1570,22 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -1587,22 +1595,22 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1612,647 +1620,647 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -2262,560 +2270,585 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
+      <c r="H90" s="15" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>DNE-62</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>3.6 TDD Lights On AU NZ</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Answer whether the overspend is AU or NZ.</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
           <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
         </is>
       </c>
-      <c r="G90" s="23" t="inlineStr"/>
-      <c r="H90" s="15" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="24" t="inlineStr">
-        <is>
-          <t>12 decisions, 8 to build, 62 done.</t>
+      <c r="G91" s="23" t="inlineStr"/>
+      <c r="H91" s="10" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>13 decisions, 8 to build, 62 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="B93:H93"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B29:H29"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G91" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G92" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H93"/>
+  <dimension ref="B2:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1278,7 +1278,7 @@
     <row r="29">
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (62)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
         </is>
       </c>
     </row>
@@ -2832,23 +2832,48 @@
       <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
-    <row r="93">
-      <c r="B93" s="24" t="inlineStr">
-        <is>
-          <t>13 decisions, 8 to build, 62 done.</t>
+    <row r="92">
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr"/>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
+      <c r="H92" s="15" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="24" t="inlineStr">
+        <is>
+          <t>13 decisions, 8 to build, 63 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B94:H94"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B20:H20"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G92" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G93" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H94"/>
+  <dimension ref="B2:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (13)</t>
+          <t>NEEDS YOUR DECISION  (14)</t>
         </is>
       </c>
     </row>
@@ -1045,45 +1045,45 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>AGREED, NOT BUILT YET  (8)</t>
-        </is>
-      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>DEC-25</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Prompt drafting rules</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Prompts for the in-model tool: first person as if Lee drafted them, fully self-contained with exact cells and expected numbers, no fixes beyond the brief, screenshot mock per build prompt.</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Lee, 09/08.</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>AGREED, NOT BUILT YET  (9)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -1105,24 +1105,24 @@
       <c r="G22" s="9" t="inlineStr"/>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1134,24 +1134,24 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -1163,53 +1163,53 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
@@ -1217,24 +1217,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr"/>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -1249,17 +1253,17 @@
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1267,91 +1271,95 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F28" s="14" t="inlineStr"/>
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
-        </is>
-      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>BLD-22</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>2.9 Commercial Fuels</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Mechanically right, reads odd.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr"/>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="inlineStr"/>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>DNE-02</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>2.x lever tabs</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr"/>
@@ -1360,23 +1368,23 @@
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>67 levers live, 8.17m impact</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr"/>
@@ -1385,23 +1393,23 @@
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr"/>
@@ -1410,23 +1418,23 @@
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr"/>
@@ -1435,23 +1443,23 @@
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr"/>
@@ -1460,23 +1468,23 @@
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified row 161. Now under review, see DEC-02</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr"/>
@@ -1485,17 +1493,17 @@
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
@@ -1510,23 +1518,23 @@
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr"/>
@@ -1535,23 +1543,23 @@
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr"/>
@@ -1560,23 +1568,23 @@
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
+          <t>1.11, 1.12, 1.13 deleted</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr"/>
@@ -1585,7 +1593,7 @@
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -1595,13 +1603,13 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr"/>
@@ -1610,7 +1618,7 @@
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1620,13 +1628,13 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
+          <t>72 validations, 54 white rows</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr"/>
@@ -1635,7 +1643,7 @@
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -1645,13 +1653,13 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G44" s="22" t="inlineStr"/>
@@ -1660,23 +1668,23 @@
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
+          <t>Verified twice across all 43 sheets</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr"/>
@@ -1685,23 +1693,23 @@
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
         </is>
       </c>
       <c r="G46" s="22" t="inlineStr"/>
@@ -1710,23 +1718,23 @@
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+          <t>494,819 charged</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr"/>
@@ -1735,23 +1743,23 @@
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr"/>
@@ -1760,23 +1768,23 @@
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr"/>
@@ -1785,23 +1793,23 @@
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
         </is>
       </c>
       <c r="G50" s="22" t="inlineStr"/>
@@ -1810,23 +1818,23 @@
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr"/>
@@ -1835,23 +1843,23 @@
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
         </is>
       </c>
       <c r="G52" s="22" t="inlineStr"/>
@@ -1860,23 +1868,23 @@
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr"/>
@@ -1885,23 +1893,23 @@
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
         </is>
       </c>
       <c r="G54" s="22" t="inlineStr"/>
@@ -1910,23 +1918,23 @@
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr"/>
@@ -1935,23 +1943,23 @@
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
         </is>
       </c>
       <c r="G56" s="22" t="inlineStr"/>
@@ -1960,23 +1968,23 @@
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr"/>
@@ -1985,23 +1993,23 @@
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
         </is>
       </c>
       <c r="G58" s="22" t="inlineStr"/>
@@ -2010,23 +2018,23 @@
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+          <t>DONE: Neil Reilly in at 666,088.</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr"/>
@@ -2035,23 +2043,23 @@
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr"/>
@@ -2060,23 +2068,23 @@
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr"/>
@@ -2085,23 +2093,23 @@
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
         </is>
       </c>
       <c r="G62" s="22" t="inlineStr"/>
@@ -2110,23 +2118,23 @@
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr"/>
@@ -2135,23 +2143,23 @@
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr"/>
@@ -2160,23 +2168,23 @@
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr"/>
@@ -2185,23 +2193,23 @@
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr"/>
@@ -2210,23 +2218,23 @@
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr"/>
@@ -2235,23 +2243,23 @@
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr"/>
@@ -2260,23 +2268,23 @@
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr"/>
@@ -2285,23 +2293,23 @@
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
         </is>
       </c>
       <c r="G70" s="22" t="inlineStr"/>
@@ -2310,23 +2318,23 @@
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr"/>
@@ -2335,23 +2343,23 @@
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr"/>
@@ -2360,23 +2368,23 @@
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr"/>
@@ -2385,23 +2393,23 @@
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr"/>
@@ -2410,23 +2418,23 @@
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr"/>
@@ -2435,23 +2443,23 @@
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr"/>
@@ -2460,23 +2468,23 @@
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr"/>
@@ -2485,23 +2493,23 @@
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr"/>
@@ -2510,23 +2518,23 @@
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr"/>
@@ -2535,7 +2543,7 @@
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -2545,13 +2553,13 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr"/>
@@ -2560,23 +2568,23 @@
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr"/>
@@ -2585,23 +2593,23 @@
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
         </is>
       </c>
       <c r="G82" s="22" t="inlineStr"/>
@@ -2610,23 +2618,23 @@
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr"/>
@@ -2635,23 +2643,23 @@
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr"/>
@@ -2660,23 +2668,23 @@
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr"/>
@@ -2685,23 +2693,23 @@
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr"/>
@@ -2710,23 +2718,23 @@
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr"/>
@@ -2735,23 +2743,23 @@
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr"/>
@@ -2760,7 +2768,7 @@
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -2770,13 +2778,13 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr"/>
@@ -2785,23 +2793,23 @@
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr"/>
@@ -2810,23 +2818,23 @@
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr"/>
@@ -2835,45 +2843,95 @@
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>DNE-62</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>3.6 TDD Lights On AU NZ</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Answer whether the overspend is AU or NZ.</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr"/>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
+      <c r="H93" s="10" t="inlineStr"/>
+    </row>
     <row r="94">
-      <c r="B94" s="24" t="inlineStr">
-        <is>
-          <t>13 decisions, 8 to build, 63 done.</t>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr"/>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
+      <c r="H94" s="15" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="24" t="inlineStr">
+        <is>
+          <t>14 decisions, 9 to build, 63 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B29:H29"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G93" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H96"/>
+  <dimension ref="B2:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (14)</t>
+          <t>NEEDS YOUR DECISION  (15)</t>
         </is>
       </c>
     </row>
@@ -1074,45 +1074,45 @@
       <c r="H20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>DEC-26</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast corrected</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>v1 withdrawn as fabricated (Finance leader lines allocated to portfolios; FY27 budget used). Finance gives lights on at AU/NZ only: AU budget 78.90 / actuals 40.97, NZ 52.23 / 26.46. Layout: Portfolio | Actuals to June | July-December months. Actuals cream typed empty; months = charged/12 formula. No italics, no subheaders, ever. Awaiting Lee's example before rebuild.</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Lee, 09/08.</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1134,24 +1134,24 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -1163,24 +1163,24 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1192,53 +1192,53 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr"/>
       <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="15" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -1246,24 +1246,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1278,17 +1282,17 @@
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
@@ -1296,239 +1300,239 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>BLD-23</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Customer</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr"/>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr"/>
-      <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
@@ -1537,13 +1541,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G39" s="23" t="inlineStr"/>
+      <c r="G39" s="22" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -1553,7 +1557,7 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
@@ -1562,63 +1566,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr"/>
+      <c r="G40" s="23" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1628,22 +1632,22 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -1653,22 +1657,22 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1678,22 +1682,22 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -1703,647 +1707,647 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -2353,585 +2357,610 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
+      <c r="H94" s="15" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr"/>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
           <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr"/>
-      <c r="H94" s="15" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="24" t="inlineStr">
-        <is>
-          <t>14 decisions, 9 to build, 63 done.</t>
+      <c r="G95" s="22" t="inlineStr"/>
+      <c r="H95" s="10" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="24" t="inlineStr">
+        <is>
+          <t>15 decisions, 9 to build, 63 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B96:H96"/>
-    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B97:H97"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H97"/>
+  <dimension ref="B2:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (15)</t>
+          <t>NEEDS YOUR DECISION  (16)</t>
         </is>
       </c>
     </row>
@@ -1103,45 +1103,45 @@
       <c r="H21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>DEC-27</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>May Finance file findings</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Full Finance model gives people net cost (Staff Cost) monthly, actual/budget/forecast, AU and NZ: combined FY26 forecast 54.42 vs budget 56.98; model FY27 charge 54.54 within 0.1 of their run. YTD over 1.50 driven by recharge under-recovery, not headcount. Cost-centre tabs are the path to a legitimate per-portfolio cut, pending Lee's mapping sign-off.</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>NOTED</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Review 09/08 on Lee's upload.</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="15" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -1163,24 +1163,24 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1192,24 +1192,24 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1221,53 +1221,53 @@
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1275,24 +1275,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
@@ -1307,17 +1311,17 @@
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
@@ -1325,239 +1329,239 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F30" s="14" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>BLD-23</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>1.2 Customer</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="15" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
@@ -1566,13 +1570,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G40" s="23" t="inlineStr"/>
+      <c r="G40" s="22" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1582,7 +1586,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
@@ -1591,63 +1595,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr"/>
+      <c r="G41" s="23" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -1657,22 +1661,22 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1682,22 +1686,22 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -1707,22 +1711,22 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1732,647 +1736,647 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -2382,585 +2386,610 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr"/>
+      <c r="H95" s="10" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr"/>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
           <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
         </is>
       </c>
-      <c r="G95" s="22" t="inlineStr"/>
-      <c r="H95" s="10" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="24" t="inlineStr">
-        <is>
-          <t>15 decisions, 9 to build, 63 done.</t>
+      <c r="G96" s="22" t="inlineStr"/>
+      <c r="H96" s="15" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="24" t="inlineStr">
+        <is>
+          <t>16 decisions, 9 to build, 63 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B97:H97"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="B23:H23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H98"/>
+  <dimension ref="B2:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1134,7 +1134,7 @@
     <row r="23">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>AGREED, NOT BUILT YET  (9)</t>
+          <t>AGREED, NOT BUILT YET  (10)</t>
         </is>
       </c>
     </row>
@@ -1392,201 +1392,205 @@
       <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>BLD-24</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast v2</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Planned and mocked, not built. People-net spine, Finance AU/NZ budgets 35.23/21.75, actuals 20.01/9.40 to June, portfolio months = charge/12 with hire-month dropdowns, gross vs charged shown. Waits on: three prompts run, Lee's sign-off, Finance June/July full file.</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Mock sent 09/08; awaiting Lee's nod.</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr"/>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr"/>
-      <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
@@ -1595,13 +1599,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G41" s="23" t="inlineStr"/>
+      <c r="G41" s="22" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -1611,7 +1615,7 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
@@ -1620,63 +1624,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr"/>
+      <c r="G42" s="23" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1686,22 +1690,22 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -1711,22 +1715,22 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1736,22 +1740,22 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -1761,647 +1765,647 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
@@ -2411,585 +2415,610 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr"/>
+      <c r="H96" s="15" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
           <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
         </is>
       </c>
-      <c r="G96" s="22" t="inlineStr"/>
-      <c r="H96" s="15" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="24" t="inlineStr">
-        <is>
-          <t>16 decisions, 9 to build, 63 done.</t>
+      <c r="G97" s="22" t="inlineStr"/>
+      <c r="H97" s="10" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="24" t="inlineStr">
+        <is>
+          <t>16 decisions, 10 to build, 63 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B99:H99"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="B34:H34"/>
     <mergeCell ref="B23:H23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H99"/>
+  <dimension ref="B2:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (16)</t>
+          <t>NEEDS YOUR DECISION  (17)</t>
         </is>
       </c>
     </row>
@@ -1132,45 +1132,45 @@
       <c r="H22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>DEC-28</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>FY26 on Finance's cut</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>June TDD Pack (2) is the source; Finance's line cut (Internal Labor/Contingent/Personnel/Recharge/Staff Cost AU, People Costs NZ); budgets 0.2 row 27 = 36.2 AU / 17.6 NZ. AU 0.59 under, NZ 1.63 over, total 1.04 over; model charge within 0.30.</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Lee, 09/08. Built same day.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1192,24 +1192,24 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1221,24 +1221,24 @@
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1250,53 +1250,53 @@
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr"/>
       <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="15" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
@@ -1304,24 +1304,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
@@ -1336,17 +1340,17 @@
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr">
@@ -1354,38 +1358,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F31" s="8" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr"/>
@@ -1394,228 +1394,232 @@
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Planned and mocked, not built. People-net spine, Finance AU/NZ budgets 35.23/21.75, actuals 20.01/9.40 to June, portfolio months = charge/12 with hire-month dropdowns, gross vs charged shown. Waits on: three prompts run, Lee's sign-off, Finance June/July full file.</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Mock sent 09/08; awaiting Lee's nod.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>BLD-24</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast v2</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Done - replaced by the Finance-cut build.</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
@@ -1624,13 +1628,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G42" s="23" t="inlineStr"/>
+      <c r="G42" s="22" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
@@ -1649,63 +1653,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G43" s="22" t="inlineStr"/>
+      <c r="G43" s="23" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -1715,22 +1719,22 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1740,22 +1744,22 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -1765,22 +1769,22 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1790,647 +1794,647 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -2440,585 +2444,610 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr"/>
+      <c r="H97" s="10" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr"/>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
           <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
         </is>
       </c>
-      <c r="G97" s="22" t="inlineStr"/>
-      <c r="H97" s="10" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="24" t="inlineStr">
-        <is>
-          <t>16 decisions, 10 to build, 63 done.</t>
+      <c r="G98" s="22" t="inlineStr"/>
+      <c r="H98" s="15" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="24" t="inlineStr">
+        <is>
+          <t>17 decisions, 10 to build, 63 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B99:H99"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B100:H100"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B23:H23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G99" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H100"/>
+  <dimension ref="B2:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (17)</t>
+          <t>NEEDS YOUR DECISION  (18)</t>
         </is>
       </c>
     </row>
@@ -1161,45 +1161,45 @@
       <c r="H23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>DEC-29</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>AUD lights on + two-Junes ruling</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Presentation sheet all-AUD proven: lights-on budgets AU 78.90 / Z 52.23 = 131.12 AUD, actuals 67.43 to June. Their 0.92 NZD-AUD rate proven from their own lines. ZTDD GM_AUD sheet is an unconverted NZD duplicate - not usable. Closed actuals beat their stale June phasing: AU lands 36.58 (0.38 over), total 55.81 (2.02 over).</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Analysis + ruling 09/08.</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1221,24 +1221,24 @@
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1250,24 +1250,24 @@
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1279,53 +1279,53 @@
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
@@ -1333,24 +1333,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr">
@@ -1365,17 +1369,17 @@
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -1383,38 +1387,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F32" s="14" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr"/>
@@ -1423,228 +1423,232 @@
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>BLD-24</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast v2</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Done - replaced by the Finance-cut build.</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr"/>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr"/>
-      <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
@@ -1653,13 +1657,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G43" s="23" t="inlineStr"/>
+      <c r="G43" s="22" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -1669,7 +1673,7 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
@@ -1678,63 +1682,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr"/>
+      <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1744,22 +1748,22 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -1769,22 +1773,22 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1794,22 +1798,22 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -1819,647 +1823,647 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
@@ -2469,585 +2473,610 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G96" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr"/>
+      <c r="H98" s="15" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
           <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
         </is>
       </c>
-      <c r="G98" s="22" t="inlineStr"/>
-      <c r="H98" s="15" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="B100" s="24" t="inlineStr">
-        <is>
-          <t>17 decisions, 10 to build, 63 done.</t>
+      <c r="G99" s="22" t="inlineStr"/>
+      <c r="H99" s="10" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="24" t="inlineStr">
+        <is>
+          <t>18 decisions, 10 to build, 63 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B101:H101"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B100:H100"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G99" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H101"/>
+  <dimension ref="B2:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1481,7 +1481,7 @@
     <row r="36">
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (63)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (64)</t>
         </is>
       </c>
     </row>
@@ -3060,23 +3060,48 @@
       <c r="G99" s="22" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
-    <row r="101">
-      <c r="B101" s="24" t="inlineStr">
-        <is>
-          <t>18 decisions, 10 to build, 63 done.</t>
+    <row r="100">
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>DNE-64</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast v2</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="inlineStr"/>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr"/>
+      <c r="H100" s="15" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="24" t="inlineStr">
+        <is>
+          <t>18 decisions, 10 to build, 64 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="B102:H102"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H102"/>
+  <dimension ref="B2:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (18)</t>
+          <t>NEEDS YOUR DECISION  (19)</t>
         </is>
       </c>
     </row>
@@ -1190,45 +1190,45 @@
       <c r="H24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>AGREED, NOT BUILT YET  (10)</t>
-        </is>
-      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>DEC-30</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q rulings</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Live FX 0.83 typed input (0.92 dead). Story anchors to 50.5 allocation (+4.04 today). Vacancy hire months drive FY26 H2/FY27. Model-driven forecasts, Finance actuals only. Never 'theirs'. Exec deck to Template.pptx first-5-slides standard, native charts, MBB/Minto.</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Lee, 09/08 pm.</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr"/>
-      <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>AGREED, NOT BUILT YET  (11)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1250,24 +1250,24 @@
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1279,24 +1279,24 @@
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1308,53 +1308,53 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="15" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr">
@@ -1362,24 +1362,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -1394,17 +1398,17 @@
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -1412,38 +1416,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F33" s="8" t="inlineStr"/>
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr"/>
@@ -1452,109 +1452,117 @@
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (64)</t>
-        </is>
-      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>BLD-24</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast v2</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Done - replaced by the Finance-cut build.</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>BLD-25</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>Wave Q exec deck</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr"/>
+          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr"/>
+          <t>In flight.</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>DNE-02</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>2.x lever tabs</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr"/>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr"/>
-      <c r="H38" s="15" t="inlineStr"/>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (64)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr"/>
@@ -1563,23 +1571,23 @@
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>67 levers live, 8.17m impact</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr"/>
@@ -1588,23 +1596,23 @@
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
         </is>
       </c>
       <c r="G41" s="22" t="inlineStr"/>
@@ -1613,23 +1621,23 @@
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr"/>
@@ -1638,23 +1646,23 @@
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
         </is>
       </c>
       <c r="G43" s="22" t="inlineStr"/>
@@ -1663,23 +1671,23 @@
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified row 161. Now under review, see DEC-02</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr"/>
@@ -1688,17 +1696,17 @@
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
@@ -1713,23 +1721,23 @@
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr"/>
@@ -1738,23 +1746,23 @@
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G47" s="22" t="inlineStr"/>
@@ -1763,23 +1771,23 @@
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
+          <t>1.11, 1.12, 1.13 deleted</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr"/>
@@ -1788,7 +1796,7 @@
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1798,13 +1806,13 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr"/>
@@ -1813,7 +1821,7 @@
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -1823,13 +1831,13 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
+          <t>72 validations, 54 white rows</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr"/>
@@ -1838,7 +1846,7 @@
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1848,13 +1856,13 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G51" s="22" t="inlineStr"/>
@@ -1863,23 +1871,23 @@
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
+          <t>Verified twice across all 43 sheets</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr"/>
@@ -1888,23 +1896,23 @@
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
         </is>
       </c>
       <c r="G53" s="22" t="inlineStr"/>
@@ -1913,23 +1921,23 @@
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+          <t>494,819 charged</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr"/>
@@ -1938,23 +1946,23 @@
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
         </is>
       </c>
       <c r="G55" s="22" t="inlineStr"/>
@@ -1963,23 +1971,23 @@
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr"/>
@@ -1988,23 +1996,23 @@
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
         </is>
       </c>
       <c r="G57" s="22" t="inlineStr"/>
@@ -2013,23 +2021,23 @@
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr"/>
@@ -2038,23 +2046,23 @@
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
         </is>
       </c>
       <c r="G59" s="22" t="inlineStr"/>
@@ -2063,23 +2071,23 @@
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr"/>
@@ -2088,23 +2096,23 @@
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
         </is>
       </c>
       <c r="G61" s="22" t="inlineStr"/>
@@ -2113,23 +2121,23 @@
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr"/>
@@ -2138,23 +2146,23 @@
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
         </is>
       </c>
       <c r="G63" s="22" t="inlineStr"/>
@@ -2163,23 +2171,23 @@
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr"/>
@@ -2188,23 +2196,23 @@
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
         </is>
       </c>
       <c r="G65" s="22" t="inlineStr"/>
@@ -2213,23 +2221,23 @@
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+          <t>DONE: Neil Reilly in at 666,088.</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr"/>
@@ -2238,23 +2246,23 @@
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
         </is>
       </c>
       <c r="G67" s="22" t="inlineStr"/>
@@ -2263,23 +2271,23 @@
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr"/>
@@ -2288,23 +2296,23 @@
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
         </is>
       </c>
       <c r="G69" s="22" t="inlineStr"/>
@@ -2313,23 +2321,23 @@
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr"/>
@@ -2338,23 +2346,23 @@
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
         </is>
       </c>
       <c r="G71" s="22" t="inlineStr"/>
@@ -2363,23 +2371,23 @@
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr"/>
@@ -2388,23 +2396,23 @@
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
         </is>
       </c>
       <c r="G73" s="22" t="inlineStr"/>
@@ -2413,23 +2421,23 @@
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr"/>
@@ -2438,23 +2446,23 @@
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
         </is>
       </c>
       <c r="G75" s="22" t="inlineStr"/>
@@ -2463,23 +2471,23 @@
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr"/>
@@ -2488,23 +2496,23 @@
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
         </is>
       </c>
       <c r="G77" s="22" t="inlineStr"/>
@@ -2513,23 +2521,23 @@
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr"/>
@@ -2538,23 +2546,23 @@
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
         </is>
       </c>
       <c r="G79" s="22" t="inlineStr"/>
@@ -2563,23 +2571,23 @@
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr"/>
@@ -2588,23 +2596,23 @@
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
         </is>
       </c>
       <c r="G81" s="22" t="inlineStr"/>
@@ -2613,23 +2621,23 @@
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr"/>
@@ -2638,23 +2646,23 @@
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
         </is>
       </c>
       <c r="G83" s="22" t="inlineStr"/>
@@ -2663,23 +2671,23 @@
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr"/>
@@ -2688,23 +2696,23 @@
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
         </is>
       </c>
       <c r="G85" s="22" t="inlineStr"/>
@@ -2713,23 +2721,23 @@
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr"/>
@@ -2738,7 +2746,7 @@
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -2748,13 +2756,13 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
         </is>
       </c>
       <c r="G87" s="22" t="inlineStr"/>
@@ -2763,23 +2771,23 @@
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr"/>
@@ -2788,23 +2796,23 @@
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
         </is>
       </c>
       <c r="G89" s="22" t="inlineStr"/>
@@ -2813,23 +2821,23 @@
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr"/>
@@ -2838,23 +2846,23 @@
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
         </is>
       </c>
       <c r="G91" s="22" t="inlineStr"/>
@@ -2863,23 +2871,23 @@
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr"/>
@@ -2888,23 +2896,23 @@
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
         </is>
       </c>
       <c r="G93" s="22" t="inlineStr"/>
@@ -2913,23 +2921,23 @@
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr"/>
@@ -2938,23 +2946,23 @@
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
         </is>
       </c>
       <c r="G95" s="22" t="inlineStr"/>
@@ -2963,7 +2971,7 @@
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
@@ -2973,13 +2981,13 @@
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr"/>
@@ -2988,23 +2996,23 @@
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
         </is>
       </c>
       <c r="G97" s="22" t="inlineStr"/>
@@ -3013,23 +3021,23 @@
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr"/>
@@ -3038,23 +3046,23 @@
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr"/>
@@ -3063,45 +3071,95 @@
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>DNE-63</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr"/>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr"/>
+      <c r="H101" s="10" t="inlineStr"/>
+    </row>
     <row r="102">
-      <c r="B102" s="24" t="inlineStr">
-        <is>
-          <t>18 decisions, 10 to build, 64 done.</t>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>DNE-64</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast v2</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+        </is>
+      </c>
+      <c r="E102" s="19" t="inlineStr"/>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr"/>
+      <c r="H102" s="15" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>19 decisions, 11 to build, 64 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B102:H102"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B104:H104"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G103" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H104"/>
+  <dimension ref="B2:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (19)</t>
+          <t>NEEDS YOUR DECISION  (20)</t>
         </is>
       </c>
     </row>
@@ -1219,45 +1219,45 @@
       <c r="H25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>DEC-31</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Vacancy timing mapping</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>107 audit rows mapped to model Role IDs; FY26 H2 vacancy cost 4.35 timed vs 7.72 naive (3.36 relief); FY27 timed reduction 0.55; prompt repairs register/rollup/exec-chain defects; 3.5 untouched.</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Built 09/08 from both analyses.</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1279,24 +1279,24 @@
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1308,24 +1308,24 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1337,53 +1337,53 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -1391,24 +1391,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -1423,17 +1427,17 @@
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
@@ -1441,38 +1445,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F34" s="14" t="inlineStr"/>
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr"/>
@@ -1481,27 +1481,27 @@
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -1510,17 +1510,17 @@
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1530,208 +1530,212 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>In flight.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>In flight.</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="15" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (64)</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr"/>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
@@ -1740,13 +1744,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G46" s="23" t="inlineStr"/>
+      <c r="G46" s="22" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1756,7 +1760,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
@@ -1765,63 +1769,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G47" s="22" t="inlineStr"/>
+      <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -1831,22 +1835,22 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1856,22 +1860,22 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -1881,22 +1885,22 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1906,647 +1910,647 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -2556,610 +2560,635 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G97" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G98" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G99" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G100" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G101" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr"/>
+      <c r="H102" s="15" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>DNE-64</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>FY26 forecast v2</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr"/>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
           <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
         </is>
       </c>
-      <c r="G102" s="23" t="inlineStr"/>
-      <c r="H102" s="15" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="24" t="inlineStr">
-        <is>
-          <t>19 decisions, 11 to build, 64 done.</t>
+      <c r="G103" s="23" t="inlineStr"/>
+      <c r="H103" s="10" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>20 decisions, 11 to build, 64 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B105:H105"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B104:H104"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G103" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H105"/>
+  <dimension ref="B2:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1568,7 +1568,7 @@
     <row r="39">
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (64)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (65)</t>
         </is>
       </c>
     </row>
@@ -3172,23 +3172,48 @@
       <c r="G103" s="23" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
-    <row r="105">
-      <c r="B105" s="24" t="inlineStr">
-        <is>
-          <t>20 decisions, 11 to build, 64 done.</t>
+    <row r="104">
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>DNE-65</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast v3</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr"/>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr"/>
+      <c r="H104" s="15" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>20 decisions, 11 to build, 65 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B105:H105"/>
+    <mergeCell ref="B106:H106"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H106"/>
+  <dimension ref="B2:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1568,7 +1568,7 @@
     <row r="39">
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (65)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (66)</t>
         </is>
       </c>
     </row>
@@ -3197,23 +3197,48 @@
       <c r="G104" s="22" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
-    <row r="106">
-      <c r="B106" s="24" t="inlineStr">
-        <is>
-          <t>20 decisions, 11 to build, 65 done.</t>
+    <row r="105">
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>DNE-66</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Exec deck v1</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr"/>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr"/>
+      <c r="H105" s="10" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="24" t="inlineStr">
+        <is>
+          <t>20 decisions, 11 to build, 66 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B106:H106"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B107:H107"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H107"/>
+  <dimension ref="B2:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (20)</t>
+          <t>NEEDS YOUR DECISION  (21)</t>
         </is>
       </c>
     </row>
@@ -1248,45 +1248,45 @@
       <c r="H26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>DEC-32</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Template + language ruling</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>THE template = FY27_Budget_Update.pptx identity (Mark OT, navy 18249C, red ED0C06). Template.pptx = ideas only. 20 screenshots before rebuild. Banned word: charge. Flip-flop analysis (Hold roles with hire months) ruled in.</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Lee, 10/08. Deck v1 rejected.</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1308,24 +1308,24 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1337,24 +1337,24 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1366,53 +1366,53 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="15" t="inlineStr"/>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -1420,24 +1420,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
@@ -1452,17 +1456,17 @@
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
@@ -1470,38 +1474,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F35" s="8" t="inlineStr"/>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -1510,27 +1510,27 @@
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
@@ -1539,17 +1539,17 @@
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -1559,208 +1559,212 @@
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>In flight.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>In flight.</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (66)</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E40" s="19" t="inlineStr"/>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="inlineStr"/>
-      <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
@@ -1769,13 +1773,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G47" s="23" t="inlineStr"/>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
@@ -1794,63 +1798,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G48" s="22" t="inlineStr"/>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1860,22 +1864,22 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -1885,22 +1889,22 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1910,22 +1914,22 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -1935,647 +1939,647 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -2585,660 +2589,685 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G96" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G98" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G99" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G99" s="22" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G100" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G101" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G102" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G103" s="22" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G104" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G105" s="22" t="inlineStr"/>
+      <c r="H105" s="10" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>DNE-66</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>Exec deck v1</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr"/>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
           <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
         </is>
       </c>
-      <c r="G105" s="23" t="inlineStr"/>
-      <c r="H105" s="10" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="24" t="inlineStr">
-        <is>
-          <t>20 decisions, 11 to build, 66 done.</t>
+      <c r="G106" s="23" t="inlineStr"/>
+      <c r="H106" s="15" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>21 decisions, 11 to build, 66 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B107:H107"/>
+    <mergeCell ref="B108:H108"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G107" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H108"/>
+  <dimension ref="B2:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (21)</t>
+          <t>NEEDS YOUR DECISION  (22)</t>
         </is>
       </c>
     </row>
@@ -1277,45 +1277,45 @@
       <c r="H27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>DEC-33</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Post-vacancy model + scope creep</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Hire months verified in full. Tool also quartered 12 roles: anchor 54.43-&gt;54.12 uninstructed, 2 codes wrong, partial application, double-count in 3.7. Ruling pending: revert (recommended) or complete. Flip-flop final: 22 roles/22 FTE/4.47 full/3.90 back into FY27.</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Awaiting Lee's one-liner.</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1337,24 +1337,24 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1366,24 +1366,24 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1395,53 +1395,53 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr"/>
       <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
@@ -1449,24 +1449,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
@@ -1481,17 +1485,17 @@
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
@@ -1499,38 +1503,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F36" s="14" t="inlineStr"/>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
@@ -1539,27 +1539,27 @@
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr"/>
@@ -1568,17 +1568,17 @@
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -1588,208 +1588,212 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>In flight.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>In flight.</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="15" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (66)</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr"/>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
@@ -1798,13 +1802,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G48" s="23" t="inlineStr"/>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1814,7 +1818,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
@@ -1823,63 +1827,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr"/>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -1889,22 +1893,22 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1914,22 +1918,22 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -1939,22 +1943,22 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -1964,647 +1968,647 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -2614,660 +2618,685 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G97" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G98" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G99" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G100" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G101" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G102" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G103" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G104" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr"/>
+      <c r="H106" s="15" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>DNE-66</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Exec deck v1</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="inlineStr"/>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
           <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
         </is>
       </c>
-      <c r="G106" s="23" t="inlineStr"/>
-      <c r="H106" s="15" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="24" t="inlineStr">
-        <is>
-          <t>21 decisions, 11 to build, 66 done.</t>
+      <c r="G107" s="23" t="inlineStr"/>
+      <c r="H107" s="10" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="24" t="inlineStr">
+        <is>
+          <t>22 decisions, 11 to build, 66 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B109:H109"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B29:H29"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B108:H108"/>
-    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G107" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G108" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H109"/>
+  <dimension ref="B2:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1626,7 +1626,7 @@
     <row r="41">
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (66)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (67)</t>
         </is>
       </c>
     </row>
@@ -3280,23 +3280,48 @@
       <c r="G107" s="23" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
-    <row r="109">
-      <c r="B109" s="24" t="inlineStr">
-        <is>
-          <t>22 decisions, 11 to build, 66 done.</t>
+    <row r="108">
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>DNE-67</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast v3.1</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr"/>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr"/>
+      <c r="H108" s="15" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>22 decisions, 11 to build, 67 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B110:H110"/>
     <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B109:H109"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G108" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G109" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H110"/>
+  <dimension ref="B2:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1626,7 +1626,7 @@
     <row r="41">
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (67)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (68)</t>
         </is>
       </c>
     </row>
@@ -3305,23 +3305,48 @@
       <c r="G108" s="22" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
-    <row r="110">
-      <c r="B110" s="24" t="inlineStr">
-        <is>
-          <t>22 decisions, 11 to build, 67 done.</t>
+    <row r="109">
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>DNE-68</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Deck v2 pass one</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr"/>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr"/>
+      <c r="H109" s="10" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>22 decisions, 11 to build, 68 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B110:H110"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B111:H111"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G109" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G110" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H111"/>
+  <dimension ref="B2:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (22)</t>
+          <t>NEEDS YOUR DECISION  (23)</t>
         </is>
       </c>
     </row>
@@ -1306,45 +1306,45 @@
       <c r="H28" s="15" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>DEC-34</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Mining findings</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>FY26 exit run rate 50.53 = the allocation; FY27 overrun = hiring pipeline annualising. Floor 48.5 via two TDD-controlled levers. Z 7pc vs Ampol 49pc recharge terms. New defects: NZ FX on 11 roles, double-counted FY27 timing line, stale tab headlines.</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>NOTED</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Verified role-by-role by the mining agent 10/08.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr"/>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1366,24 +1366,24 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1395,24 +1395,24 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1424,53 +1424,53 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr"/>
       <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
@@ -1478,24 +1478,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
@@ -1510,17 +1514,17 @@
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -1528,38 +1532,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr"/>
@@ -1568,27 +1568,27 @@
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr"/>
@@ -1597,17 +1597,17 @@
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1617,208 +1617,212 @@
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>In flight.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="B41" s="21" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>In flight.</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (68)</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr"/>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr"/>
-      <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
@@ -1827,13 +1831,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G49" s="23" t="inlineStr"/>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
@@ -1852,63 +1856,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G50" s="22" t="inlineStr"/>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1918,22 +1922,22 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -1943,22 +1947,22 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -1968,22 +1972,22 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -1993,647 +1997,647 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -2643,710 +2647,735 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G96" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G98" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G99" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G99" s="22" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G100" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G101" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G102" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G103" s="22" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G104" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G105" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G105" s="22" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="inlineStr"/>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
-        </is>
-      </c>
-      <c r="G108" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-67</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>FY26 forecast v3.1</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr"/>
+      <c r="H109" s="10" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>DNE-68</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>Deck v2 pass one</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr"/>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
           <t>Shipped 10/08 after independent QA.</t>
         </is>
       </c>
-      <c r="G109" s="23" t="inlineStr"/>
-      <c r="H109" s="10" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="24" t="inlineStr">
-        <is>
-          <t>22 decisions, 11 to build, 68 done.</t>
+      <c r="G110" s="23" t="inlineStr"/>
+      <c r="H110" s="15" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>23 decisions, 11 to build, 68 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B111:H111"/>
-    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B112:H112"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G110" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G111" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H112"/>
+  <dimension ref="B2:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -1655,7 +1655,7 @@
     <row r="42">
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (68)</t>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (69)</t>
         </is>
       </c>
     </row>
@@ -3359,23 +3359,48 @@
       <c r="G110" s="23" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
     </row>
-    <row r="112">
-      <c r="B112" s="24" t="inlineStr">
-        <is>
-          <t>23 decisions, 11 to build, 68 done.</t>
+    <row r="111">
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>DNE-69</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Deck v2 final</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr"/>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Shipped 10/08 after redirect + QA.</t>
+        </is>
+      </c>
+      <c r="G111" s="22" t="inlineStr"/>
+      <c r="H111" s="10" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>23 decisions, 11 to build, 69 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B113:H113"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B30:H30"/>
-    <mergeCell ref="B112:H112"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G111" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G112" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H113"/>
+  <dimension ref="B2:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (23)</t>
+          <t>NEEDS YOUR DECISION  (24)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>FY26 exit run rate 50.53 = the allocation; FY27 overrun = hiring pipeline annualising. Floor 48.5 via two TDD-controlled levers. Z 7pc vs Ampol 49pc recharge terms. New defects: NZ FX on 11 roles, double-counted FY27 timing line, stale tab headlines.</t>
+          <t>FY26 December exit run rate 52.23 annualised - derivable both sides of the pending quarter-code ruling (the 50.53 first cut did not reproduce and is superseded); FY27 overrun = the hiring pipeline annualising. 48.50 via the two reductions of cost TDD controls (hold the 19 vacant overhead roles; offshore the last 21 onshore roles in marked squads, 0.92 landing on what TDD pays). New defects: NZ FX on 11 roles, double-counted FY27 timing line, stale tab headlines, 3.10 Saving labels.</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
@@ -1328,52 +1328,52 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Verified role-by-role by the mining agent 10/08.</t>
+          <t>Mined 10/08; exit number corrected in the compliance loop 10/08 pm.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>DEC-35</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Saving banned</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Nothing is a saving - it is a reduction of cost. Banned in every form (saving, savings, saves, saved) across the deck, the models, the FY26 workbook, prompts and chat. Say cost reduction / reduction of cost / takes cost out. The model 3.10 labels carry the word - queued for the next in-model fix prompt.</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Lee 10/08 pm.</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1395,24 +1395,24 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1424,24 +1424,24 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1453,53 +1453,53 @@
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr"/>
       <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
@@ -1507,24 +1507,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr"/>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -1539,17 +1543,17 @@
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
@@ -1557,38 +1561,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F38" s="14" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr"/>
@@ -1597,27 +1597,27 @@
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr"/>
@@ -1626,17 +1626,17 @@
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Analysis agents running (model f4ce93da, vacancy audit, 3 decks, MBB research). Then: vacancy prompt to the in-model tool, FY26 v3 workbook, deck build with options, QA loops.</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1646,208 +1646,212 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>In flight.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Deck v2 built in Lee's file (22 slides, 14 native charts). Compliance loop running: formatting normalised to the slides 2-4 standard + reorder to story order; 14-fix round from the 18-item audit (offshore split corrected to 13.59/5.19, exit story rebuilt on 52.23, NZ Finance column 2.40/26.94, saving-language sweep); full-transcript re-read of every instruction. FY26 v3.1 workbook verified whole - all checks pass.</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Fix round in flight; nothing ships below standard.</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="15" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (69)</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
@@ -1856,13 +1860,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G50" s="23" t="inlineStr"/>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1872,7 +1876,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
@@ -1881,63 +1885,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G51" s="22" t="inlineStr"/>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -1947,22 +1951,22 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -1972,22 +1976,22 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -1997,22 +2001,22 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2022,647 +2026,647 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -2672,735 +2676,760 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G97" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G98" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G99" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G100" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G101" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G102" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G103" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G104" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G106" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G107" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
-        </is>
-      </c>
-      <c r="G108" s="23" t="inlineStr"/>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
-        </is>
-      </c>
-      <c r="G109" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr"/>
       <c r="H109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-67</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>FY26 forecast v3.1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr"/>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after independent QA.</t>
-        </is>
-      </c>
-      <c r="G110" s="23" t="inlineStr"/>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>DNE-69</t>
+          <t>DNE-68</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 final</t>
+          <t>Deck v2 pass one</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="8" t="inlineStr">
         <is>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr"/>
+      <c r="H111" s="10" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>DNE-69</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Deck v2 final</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr"/>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
           <t>Shipped 10/08 after redirect + QA.</t>
         </is>
       </c>
-      <c r="G111" s="22" t="inlineStr"/>
-      <c r="H111" s="10" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>23 decisions, 11 to build, 69 done.</t>
+      <c r="G112" s="22" t="inlineStr"/>
+      <c r="H112" s="15" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>24 decisions, 11 to build, 69 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B113:H113"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="B42:H42"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B114:H114"/>
+    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G112" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G113" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H114"/>
+  <dimension ref="B2:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (24)</t>
+          <t>NEEDS YOUR DECISION  (25)</t>
         </is>
       </c>
     </row>
@@ -1364,45 +1364,45 @@
       <c r="H30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>DEC-36</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>FY26 landing corrected to 53.72</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>The second half runs on what TDD pays: relief = each priced vacancy times its squad support percentage (1.99, never the gross 3.10), base = everyone at a full year 54.4290. Landings AU 37.68 / NZ 16.04 / total 53.72 - 3.22 over the 50.5 allocation, 0.08 inside the 53.8 budget. H2 25.22 annualising 50.45; December exit 53.27. Independent of the start-quarter ruling. Supersedes 52.45 and every earlier exit number.</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Found in QA 10/08 pm; rebuilt role by role, verified to 4dp.</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr"/>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1424,24 +1424,24 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1453,24 +1453,24 @@
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1482,53 +1482,53 @@
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr"/>
       <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="15" t="inlineStr"/>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -1536,24 +1536,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
@@ -1568,17 +1572,17 @@
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -1586,38 +1590,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F39" s="8" t="inlineStr"/>
       <c r="G39" s="9" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E40" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr"/>
@@ -1626,27 +1626,27 @@
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr"/>
@@ -1655,17 +1655,17 @@
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 built in Lee's file (22 slides, 14 native charts). Compliance loop running: formatting normalised to the slides 2-4 standard + reorder to story order; 14-fix round from the 18-item audit (offshore split corrected to 13.59/5.19, exit story rebuilt on 52.23, NZ Finance column 2.40/26.94, saving-language sweep); full-transcript re-read of every instruction. FY26 v3.1 workbook verified whole - all checks pass.</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1675,208 +1675,212 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Fix round in flight; nothing ships below standard.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="B43" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (69)</t>
-        </is>
-      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Delivered with the compliance summary and cull list.</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr"/>
-      <c r="H44" s="15" t="inlineStr"/>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (70)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
@@ -1885,13 +1889,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G51" s="23" t="inlineStr"/>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -1901,7 +1905,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
@@ -1910,63 +1914,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G52" s="22" t="inlineStr"/>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -1976,22 +1980,22 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -2001,22 +2005,22 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2026,22 +2030,22 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -2051,647 +2055,647 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -2701,735 +2705,785 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G96" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G98" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G99" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G99" s="22" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G100" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G101" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G102" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G103" s="22" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G104" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G105" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G105" s="22" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G108" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="inlineStr"/>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr"/>
       <c r="H109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr"/>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
-        </is>
-      </c>
-      <c r="G110" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-67</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>FY26 forecast v3.1</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after independent QA.</t>
-        </is>
-      </c>
-      <c r="G111" s="23" t="inlineStr"/>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G111" s="22" t="inlineStr"/>
       <c r="H111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>DNE-69</t>
+          <t>DNE-68</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 final</t>
+          <t>Deck v2 pass one</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr"/>
       <c r="F112" s="14" t="inlineStr">
         <is>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G112" s="23" t="inlineStr"/>
+      <c r="H112" s="15" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>DNE-69</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Deck v2 final</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="inlineStr"/>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
           <t>Shipped 10/08 after redirect + QA.</t>
         </is>
       </c>
-      <c r="G112" s="22" t="inlineStr"/>
-      <c r="H112" s="15" t="inlineStr"/>
+      <c r="G113" s="22" t="inlineStr"/>
+      <c r="H113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="B114" s="24" t="inlineStr">
-        <is>
-          <t>24 decisions, 11 to build, 69 done.</t>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>DNE-70</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Wave Q package</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+        </is>
+      </c>
+      <c r="E114" s="19" t="inlineStr"/>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr"/>
+      <c r="H114" s="15" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>25 decisions, 11 to build, 70 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B116:H116"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B114:H114"/>
-    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G113" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G115" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H116"/>
+  <dimension ref="B2:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (25)</t>
+          <t>NEEDS YOUR DECISION  (26)</t>
         </is>
       </c>
     </row>
@@ -1393,45 +1393,49 @@
       <c r="H31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>DEC-37</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Deck standard finalised</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Lee's finalised Ampol FY27 Budget Update deck is now THE reference for every slide: language, structure, formatting. Mark OT fonts, navy 18249C with red ED0C06 rationed to over-budget numbers and callouts, action titles as full sentences carrying the number, Insight &amp; Assumptions rail on the right ~25%, navy-header tables with a labelled total row, native editable charts, notes as the full spoken narrative. Captured in docs/DECK_STANDARD.md with measured geometry; the deck itself kept at reference/Ampol_FY27_Budget_Update_FINAL.pptx.</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Extracted from his upload 18/08: 8 slides read, rendered and measured; theme, palette, fonts and shape geometry taken from the XML, not eyeballed.</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>as a note, this is what i finalised. save as memory for language, slide structure, formatting and for reference of all my slides going forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr"/>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -1441,7 +1445,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1453,24 +1457,24 @@
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1482,24 +1486,24 @@
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1511,53 +1515,53 @@
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
@@ -1565,24 +1569,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -1597,17 +1605,17 @@
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
@@ -1615,38 +1623,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F40" s="14" t="inlineStr"/>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr"/>
@@ -1655,27 +1659,27 @@
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr"/>
@@ -1684,228 +1688,232 @@
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>DONE</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Delivered with the compliance summary and cull list.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Delivered with the compliance summary and cull list.</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr"/>
+      <c r="H44" s="15" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (70)</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr"/>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
@@ -1914,13 +1922,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G52" s="23" t="inlineStr"/>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1930,7 +1938,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
@@ -1939,63 +1947,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G53" s="22" t="inlineStr"/>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -2005,22 +2013,22 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2030,22 +2038,22 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -2055,22 +2063,22 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -2080,647 +2088,647 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -2730,760 +2738,785 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G97" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G98" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G99" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G100" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G101" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G102" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G103" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G104" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G106" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G107" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G108" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G109" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr"/>
       <c r="H109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr"/>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
-        </is>
-      </c>
-      <c r="G110" s="23" t="inlineStr"/>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
-        </is>
-      </c>
-      <c r="G111" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr"/>
       <c r="H111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-67</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>FY26 forecast v3.1</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr"/>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after independent QA.</t>
-        </is>
-      </c>
-      <c r="G112" s="23" t="inlineStr"/>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr"/>
       <c r="H112" s="15" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>DNE-69</t>
+          <t>DNE-68</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 final</t>
+          <t>Deck v2 pass one</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr"/>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after redirect + QA.</t>
-        </is>
-      </c>
-      <c r="G113" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr"/>
       <c r="H113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>DNE-70</t>
+          <t>DNE-69</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>Wave Q package</t>
+          <t>Deck v2 final</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr"/>
       <c r="F114" s="14" t="inlineStr">
         <is>
+          <t>Shipped 10/08 after redirect + QA.</t>
+        </is>
+      </c>
+      <c r="G114" s="22" t="inlineStr"/>
+      <c r="H114" s="15" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>DNE-70</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q package</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr"/>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
           <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
         </is>
       </c>
-      <c r="G114" s="23" t="inlineStr"/>
-      <c r="H114" s="15" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="B116" s="24" t="inlineStr">
-        <is>
-          <t>25 decisions, 11 to build, 70 done.</t>
+      <c r="G115" s="23" t="inlineStr"/>
+      <c r="H115" s="10" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>26 decisions, 11 to build, 70 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B116:H116"/>
+    <mergeCell ref="B117:H117"/>
+    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B45:H45"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G115" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G116" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H117"/>
+  <dimension ref="B2:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (26)</t>
+          <t>NEEDS YOUR DECISION  (27)</t>
         </is>
       </c>
     </row>
@@ -1426,45 +1426,49 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>DEC-38</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Non-labour mapping build</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Green-lit build of the non-labour mapping workbook: 49,910 AU HW/SW leaf lines placed by portfolio and platform, six open calls as live dropdowns (proposals loaded, marked), profile with labour beside non-labour and a zero check, reconciliation bridge to roughly 302 with named TBC blocks, raw tabs verbatim. Leaf total 76,757,132.79 proven; profile holds it under every decision branch.</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Profile engine verified independently in python for both branches of all six decisions; Enterprise Data nets to zero on current tells and is flagged, not plugged.</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>sweet build</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -1474,7 +1478,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1486,24 +1490,24 @@
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1515,24 +1519,24 @@
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1544,53 +1548,53 @@
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="15" t="inlineStr"/>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -1598,24 +1602,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G39" s="9" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
@@ -1630,17 +1638,17 @@
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
@@ -1648,38 +1656,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F41" s="8" t="inlineStr"/>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr"/>
@@ -1688,27 +1692,27 @@
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr"/>
@@ -1717,228 +1721,232 @@
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>DONE</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Delivered with the compliance summary and cull list.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Delivered with the compliance summary and cull list.</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (70)</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr"/>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G46" s="22" t="inlineStr"/>
-      <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
@@ -1947,13 +1955,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G53" s="23" t="inlineStr"/>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -1963,7 +1971,7 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
@@ -1972,63 +1980,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G54" s="22" t="inlineStr"/>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2038,22 +2046,22 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -2063,22 +2071,22 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -2088,22 +2096,22 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
@@ -2113,647 +2121,647 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -2763,760 +2771,785 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G96" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G98" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G99" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G99" s="22" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G100" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G101" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G102" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G103" s="22" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G104" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G105" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G105" s="22" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G108" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr"/>
       <c r="H109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr"/>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G110" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
-        </is>
-      </c>
-      <c r="G111" s="23" t="inlineStr"/>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G111" s="22" t="inlineStr"/>
       <c r="H111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr"/>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
-        </is>
-      </c>
-      <c r="G112" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G112" s="23" t="inlineStr"/>
       <c r="H112" s="15" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-67</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>FY26 forecast v3.1</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr"/>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after independent QA.</t>
-        </is>
-      </c>
-      <c r="G113" s="23" t="inlineStr"/>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G113" s="22" t="inlineStr"/>
       <c r="H113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>DNE-69</t>
+          <t>DNE-68</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 final</t>
+          <t>Deck v2 pass one</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr"/>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after redirect + QA.</t>
-        </is>
-      </c>
-      <c r="G114" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr"/>
       <c r="H114" s="15" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>DNE-70</t>
+          <t>DNE-69</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Wave Q package</t>
+          <t>Deck v2 final</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr"/>
       <c r="F115" s="8" t="inlineStr">
         <is>
+          <t>Shipped 10/08 after redirect + QA.</t>
+        </is>
+      </c>
+      <c r="G115" s="22" t="inlineStr"/>
+      <c r="H115" s="10" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>DNE-70</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>Wave Q package</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+        </is>
+      </c>
+      <c r="E116" s="19" t="inlineStr"/>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
           <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
         </is>
       </c>
-      <c r="G115" s="23" t="inlineStr"/>
-      <c r="H115" s="10" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="24" t="inlineStr">
-        <is>
-          <t>26 decisions, 11 to build, 70 done.</t>
+      <c r="G116" s="23" t="inlineStr"/>
+      <c r="H116" s="15" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>27 decisions, 11 to build, 70 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B118:H118"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B117:H117"/>
-    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G116" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G117" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H118"/>
+  <dimension ref="B2:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (27)</t>
+          <t>NEEDS YOUR DECISION  (28)</t>
         </is>
       </c>
     </row>
@@ -1459,45 +1459,49 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>DEC-39</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Evidence-based non-labour mapping shipped</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>49,910 lines read and placed or honestly opened: Placed 55.44m, Sig funded 13.68m, Open 7.64m in named families. His five tabs byte-identical by hash; four value-only tabs added. Nine items on his decision list, led by the 6.87m device catalogue where his SW grammar and his budget mapping disagree.</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Six readers, deep pass, adversary, consistency auditor, integration builder; independent audits at every gate; all sums tie to 76,757,132.79 to the cent.</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>i need perfection, no assumptions, not one assumption to be made</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>BLD-11</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Whole model</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -1507,7 +1511,7 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1519,24 +1523,24 @@
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-20</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1548,24 +1552,24 @@
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -1577,53 +1581,53 @@
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr"/>
       <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
@@ -1631,24 +1635,28 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr"/>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
+        </is>
+      </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
@@ -1663,17 +1671,17 @@
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
@@ -1681,38 +1689,34 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>Mechanically right, reads odd.</t>
-        </is>
-      </c>
+      <c r="F42" s="14" t="inlineStr"/>
       <c r="G42" s="9" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr"/>
@@ -1721,27 +1725,27 @@
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-23</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Done - replaced by the Finance-cut build.</t>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr"/>
@@ -1750,228 +1754,232 @@
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>DONE</t>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Delivered with the compliance summary and cull list.</t>
+          <t>Done - replaced by the Finance-cut build.</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>BLD-25</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Wave Q exec deck</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Delivered with the compliance summary and cull list.</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>DONE AND VERIFIED IN THE SHIPPED FILE  (70)</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>DNE-01</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>2.3 Enterprise Data</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr"/>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr"/>
-      <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
@@ -1980,13 +1988,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G54" s="23" t="inlineStr"/>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -1996,7 +2004,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
@@ -2005,63 +2013,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G55" s="22" t="inlineStr"/>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -2071,22 +2079,22 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -2096,22 +2104,22 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
@@ -2121,22 +2129,22 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -2146,647 +2154,647 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G61" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G63" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G67" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -2796,760 +2804,785 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G87" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G89" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G91" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G97" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G98" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G99" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G100" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G101" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G102" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G103" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G104" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G106" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G107" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G108" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G109" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr"/>
       <c r="H109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr"/>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G110" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G111" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr"/>
       <c r="H111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr"/>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
-        </is>
-      </c>
-      <c r="G112" s="23" t="inlineStr"/>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr"/>
       <c r="H112" s="15" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr"/>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
-        </is>
-      </c>
-      <c r="G113" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr"/>
       <c r="H113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-67</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>FY26 forecast v3.1</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr"/>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after independent QA.</t>
-        </is>
-      </c>
-      <c r="G114" s="23" t="inlineStr"/>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G114" s="22" t="inlineStr"/>
       <c r="H114" s="15" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>DNE-69</t>
+          <t>DNE-68</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 final</t>
+          <t>Deck v2 pass one</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr"/>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after redirect + QA.</t>
-        </is>
-      </c>
-      <c r="G115" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr"/>
       <c r="H115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>DNE-70</t>
+          <t>DNE-69</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Wave Q package</t>
+          <t>Deck v2 final</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
         </is>
       </c>
       <c r="E116" s="19" t="inlineStr"/>
       <c r="F116" s="14" t="inlineStr">
         <is>
+          <t>Shipped 10/08 after redirect + QA.</t>
+        </is>
+      </c>
+      <c r="G116" s="22" t="inlineStr"/>
+      <c r="H116" s="15" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>DNE-70</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q package</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr"/>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
           <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
         </is>
       </c>
-      <c r="G116" s="23" t="inlineStr"/>
-      <c r="H116" s="15" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="24" t="inlineStr">
-        <is>
-          <t>27 decisions, 11 to build, 70 done.</t>
+      <c r="G117" s="23" t="inlineStr"/>
+      <c r="H117" s="10" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>28 decisions, 11 to build, 70 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B118:H118"/>
+    <mergeCell ref="B119:H119"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B47:H47"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G117" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G118" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H119"/>
+  <dimension ref="B2:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (28)</t>
+          <t>NEEDS YOUR DECISION  (31)</t>
         </is>
       </c>
     </row>
@@ -1492,103 +1492,103 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>DEC-40</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>FY27 dashboard</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Enterprise Data has a 0.50m group tagged sig items with no funding against it; it sits in the portfolio's own cost and shows as still to fund in the Squad cost block. Confirm that is right or name the funding.</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Flagged 28/08 with the option pack; carried into the rebuilt portfolio tab, never plugged.</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>BLD-11</t>
+          <t>DEC-41</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>FY27 cost model</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr"/>
+          <t>The column Q fix left three stale spots in the model: the written bridges (3.5 rows 30 to 32, 3.8 rows 34 to 38) are out by the 8.80 allocated overheads, and the 3.8 title cell still carries 99.36/54.43. The in-model fix prompt is drafted on request.</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Knock-ons of the column Q change, verified 28/08; the model computes right, only the words and the title are stale.</t>
+        </is>
+      </c>
       <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="15" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
-        </is>
-      </c>
+      <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>DEC-42</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Role mapping hygiene</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr"/>
+          <t>REVIEW carries platform NA on 75 rows (14.30m), no platform on 20 rows (3.75m), and AMPOS and AmPOS as two spellings. Kept visible as their own rows on the Cost per FTE tab per the raw data rule. Clean them in the model, or keep as is?</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Surfaced by the cost per FTE view 28/08; nothing merged or plugged.</t>
+        </is>
+      </c>
       <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
-        </is>
-      </c>
+      <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>BLD-20</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>COE tabs</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr"/>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="15" t="inlineStr">
-        <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>AGREED, NOT BUILT YET  (12)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -1610,103 +1610,111 @@
       <c r="G39" s="9" t="inlineStr"/>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr"/>
       <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="15" t="inlineStr"/>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr"/>
       <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr"/>
       <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="15" t="inlineStr"/>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
@@ -1716,7 +1724,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Mechanically right, reads odd.</t>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr"/>
@@ -1725,217 +1733,229 @@
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
-        </is>
-      </c>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="9" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Done - replaced by the Finance-cut build.</t>
-        </is>
-      </c>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr"/>
       <c r="G45" s="9" t="inlineStr"/>
       <c r="H45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>DONE</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Delivered with the compliance summary and cull list.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="B47" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (70)</t>
-        </is>
-      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>BLD-23</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Customer</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr"/>
+      <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E48" s="19" t="inlineStr"/>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr"/>
+          <t>Done - replaced by the Finance-cut build.</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>BLD-25</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>Wave Q exec deck</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr"/>
+          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr"/>
+          <t>Delivered with the compliance summary and cull list.</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>BLD-26</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>FY27 dashboard rebuild</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
-        </is>
-      </c>
-      <c r="E50" s="19" t="inlineStr"/>
+          <t>Revert to the original dashboard on the new model; portfolio tabs get the overheads KPI band and typed sentence per the markup, the platform grouped squad chart, platform cost chart and FTE chart, and the Squad cost block; Lever mix and Cost per FTE added as new tabs.</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr"/>
-      <c r="H50" s="15" t="inlineStr"/>
+          <t>Ruled 28/08 on the option pack; build running through the agent loop with recalc, checks and renders before it ships.</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>let's revert to the original dashboard... add option 7 as additive... option 4 bar chart should be added as additive to the portfolio tabs</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>DNE-04</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>0.1 and 1.2</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="inlineStr"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr"/>
-      <c r="H51" s="10" t="inlineStr"/>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (70)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
         </is>
       </c>
       <c r="G52" s="22" t="inlineStr"/>
@@ -1944,23 +1964,23 @@
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
+          <t>67 levers live, 8.17m impact</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr"/>
@@ -1969,23 +1989,23 @@
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
         </is>
       </c>
       <c r="G54" s="22" t="inlineStr"/>
@@ -1994,17 +2014,17 @@
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
@@ -2019,23 +2039,23 @@
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
         </is>
       </c>
       <c r="G56" s="22" t="inlineStr"/>
@@ -2044,23 +2064,23 @@
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
+          <t>Verified row 161. Now under review, see DEC-02</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr"/>
@@ -2069,23 +2089,23 @@
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G58" s="22" t="inlineStr"/>
@@ -2094,23 +2114,23 @@
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr"/>
@@ -2119,17 +2139,17 @@
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
@@ -2144,23 +2164,23 @@
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
+          <t>1.11, 1.12, 1.13 deleted</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr"/>
@@ -2169,7 +2189,7 @@
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
@@ -2179,13 +2199,13 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
         </is>
       </c>
       <c r="G62" s="22" t="inlineStr"/>
@@ -2194,23 +2214,23 @@
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
+          <t>72 validations, 54 white rows</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr"/>
@@ -2219,23 +2239,23 @@
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr"/>
@@ -2244,23 +2264,23 @@
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+          <t>Verified twice across all 43 sheets</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr"/>
@@ -2269,23 +2289,23 @@
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr"/>
@@ -2294,23 +2314,23 @@
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+          <t>494,819 charged</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr"/>
@@ -2319,23 +2339,23 @@
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr"/>
@@ -2344,23 +2364,23 @@
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr"/>
@@ -2369,23 +2389,23 @@
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
         </is>
       </c>
       <c r="G70" s="22" t="inlineStr"/>
@@ -2394,23 +2414,23 @@
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr"/>
@@ -2419,23 +2439,23 @@
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr"/>
@@ -2444,23 +2464,23 @@
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr"/>
@@ -2469,23 +2489,23 @@
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr"/>
@@ -2494,23 +2514,23 @@
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr"/>
@@ -2519,23 +2539,23 @@
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr"/>
@@ -2544,23 +2564,23 @@
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr"/>
@@ -2569,23 +2589,23 @@
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr"/>
@@ -2594,23 +2614,23 @@
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+          <t>DONE: Neil Reilly in at 666,088.</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr"/>
@@ -2619,23 +2639,23 @@
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr"/>
@@ -2644,23 +2664,23 @@
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr"/>
@@ -2669,23 +2689,23 @@
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
         </is>
       </c>
       <c r="G82" s="22" t="inlineStr"/>
@@ -2694,23 +2714,23 @@
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr"/>
@@ -2719,23 +2739,23 @@
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr"/>
@@ -2744,23 +2764,23 @@
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr"/>
@@ -2769,23 +2789,23 @@
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr"/>
@@ -2794,23 +2814,23 @@
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr"/>
@@ -2819,23 +2839,23 @@
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr"/>
@@ -2844,23 +2864,23 @@
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr"/>
@@ -2869,23 +2889,23 @@
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr"/>
@@ -2894,23 +2914,23 @@
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr"/>
@@ -2919,23 +2939,23 @@
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr"/>
@@ -2944,23 +2964,23 @@
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr"/>
@@ -2969,23 +2989,23 @@
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr"/>
@@ -2994,23 +3014,23 @@
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr"/>
@@ -3019,23 +3039,23 @@
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr"/>
@@ -3044,23 +3064,23 @@
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr"/>
@@ -3069,23 +3089,23 @@
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr"/>
@@ -3094,23 +3114,23 @@
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr"/>
@@ -3119,23 +3139,23 @@
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr"/>
@@ -3144,23 +3164,23 @@
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr"/>
@@ -3169,7 +3189,7 @@
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
@@ -3179,13 +3199,13 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr"/>
@@ -3194,23 +3214,23 @@
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr"/>
@@ -3219,23 +3239,23 @@
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr"/>
@@ -3244,23 +3264,23 @@
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr"/>
@@ -3269,23 +3289,23 @@
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr"/>
@@ -3294,23 +3314,23 @@
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr"/>
@@ -3319,23 +3339,23 @@
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr"/>
@@ -3344,23 +3364,23 @@
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr"/>
@@ -3369,23 +3389,23 @@
     <row r="110">
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr"/>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr"/>
@@ -3394,23 +3414,23 @@
     <row r="111">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr"/>
@@ -3419,23 +3439,23 @@
     <row r="112">
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr"/>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr"/>
@@ -3444,23 +3464,23 @@
     <row r="113">
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr"/>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr"/>
@@ -3469,23 +3489,23 @@
     <row r="114">
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr"/>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr"/>
@@ -3494,23 +3514,23 @@
     <row r="115">
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr"/>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after independent QA.</t>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr"/>
@@ -3519,23 +3539,23 @@
     <row r="116">
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>DNE-69</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 final</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E116" s="19" t="inlineStr"/>
       <c r="F116" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after redirect + QA.</t>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr"/>
@@ -3544,45 +3564,145 @@
     <row r="117">
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>DNE-70</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Wave Q package</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E117" s="18" t="inlineStr"/>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr"/>
       <c r="H117" s="10" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>DNE-67</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>FY26 forecast v3.1</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="inlineStr"/>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr"/>
+      <c r="H118" s="15" t="inlineStr"/>
+    </row>
     <row r="119">
-      <c r="B119" s="24" t="inlineStr">
-        <is>
-          <t>28 decisions, 11 to build, 70 done.</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>DNE-68</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Deck v2 pass one</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr"/>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr"/>
+      <c r="H119" s="10" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>DNE-69</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Deck v2 final</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+        </is>
+      </c>
+      <c r="E120" s="19" t="inlineStr"/>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>Shipped 10/08 after redirect + QA.</t>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr"/>
+      <c r="H120" s="15" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>DNE-70</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Wave Q package</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+        </is>
+      </c>
+      <c r="E121" s="18" t="inlineStr"/>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr"/>
+      <c r="H121" s="10" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>31 decisions, 12 to build, 70 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B119:H119"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B123:H123"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B51:H51"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G118" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G122" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1581,7 +1581,7 @@
     <row r="38">
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>AGREED, NOT BUILT YET  (12)</t>
+          <t>AGREED, NOT BUILT YET  (11)</t>
         </is>
       </c>
     </row>
@@ -1897,209 +1897,201 @@
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>BLD-26</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>FY27 dashboard rebuild</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>Revert to the original dashboard on the new model; portfolio tabs get the overheads KPI band and typed sentence per the markup, the platform grouped squad chart, platform cost chart and FTE chart, and the Squad cost block; Lever mix and Cost per FTE added as new tabs.</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>Ruled 28/08 on the option pack; build running through the agent loop with recalc, checks and renders before it ships.</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="15" t="inlineStr">
-        <is>
-          <t>let's revert to the original dashboard... add option 7 as additive... option 4 bar chart should be added as additive to the portfolio tabs</t>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (71)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (70)</t>
-        </is>
-      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>DNE-01</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>2.3 Enterprise Data</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr"/>
+      <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-03</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-08</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
@@ -2108,13 +2100,13 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G58" s="22" t="inlineStr"/>
+      <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-09</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -2124,7 +2116,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
@@ -2133,63 +2125,63 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G59" s="23" t="inlineStr"/>
+      <c r="G59" s="22" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-10</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr"/>
+          <t>1.11, 1.12, 1.13 deleted</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-11</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>No sheet or workbook protection anywhere</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>1.11, 1.12, 1.13 deleted</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr"/>
+          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr"/>
       <c r="H61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>DNE-11</t>
+          <t>DNE-12</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
@@ -2199,22 +2191,22 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>No sheet or workbook protection anywhere</t>
+          <t>Strict dropdowns instead of protection, controls kept in white font</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>SUPERSEDED: you asked for protection after this, and on 05/08 for it only where nobody types. Where it landed: the 0.x and 3.x tabs protected, every other tab open.</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr"/>
+          <t>72 validations, 54 white rows</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DNE-12</t>
+          <t>DNE-13</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -2224,22 +2216,22 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Strict dropdowns instead of protection, controls kept in white font</t>
+          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>72 validations, 54 white rows</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr"/>
       <c r="H63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>DNE-13</t>
+          <t>DNE-14</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
@@ -2249,22 +2241,22 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Your language and wording kept from both the 30/07 and 13/07 files</t>
+          <t>The word wave appears nowhere</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="inlineStr"/>
+          <t>Verified twice across all 43 sheets</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DNE-14</t>
+          <t>DNE-15</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -2274,647 +2266,647 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>The word wave appears nowhere</t>
+          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Verified twice across all 43 sheets</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr"/>
+          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr"/>
       <c r="H65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>DNE-15</t>
+          <t>DNE-16</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Funded outside TDD architecture: Lists table, P and Q columns on every 2.x, split on 3.1</t>
+          <t>Cyber uplift percentage column feeding 1.14</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>EGI 11.88, CTRM 3.80, AmPOS 1.40, uplift 1.30</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr"/>
+          <t>494,819 charged</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DNE-16</t>
+          <t>DNE-17</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Cyber uplift percentage column feeding 1.14</t>
+          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>494,819 charged</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr"/>
+          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr"/>
       <c r="H67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DNE-17</t>
+          <t>DNE-18</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>1.3 Enterprise Data</t>
+          <t>1.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Add the EGI Ent Data platform and squad line carrying 1.8119, live from 2.3, and net it...</t>
+          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.3 carries Platform: EGI Ent Data with the 1.8119 live from 2.3; Significant Items EGI reads it; gate C 8/8.</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="inlineStr"/>
+          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>DNE-18</t>
+          <t>DNE-19</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>1.1 Ampol Retail</t>
+          <t>1.4 TDD Group Functions</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>EGI line must include the EGI TDD squad: 1.2214 becomes 1.5211.</t>
+          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>DONE as ruled after the Viren move: 1.1 EGI line = EGI Retail 1.2214 live (Viren now on 2.4); gate C.</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr"/>
+          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DNE-19</t>
+          <t>DNE-20</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>1.4 TDD Group Functions</t>
+          <t>2.12 and 2.13 COE</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Relabel Funded from TDD Corporate pool (3.4 COE Breakdown) to EGI. 3.4 carries no such ...</t>
+          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.4 line relabelled Significant Items EGI reading 2.4's EGI TDD funded 1.3245 live; gate C.</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr"/>
+          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>DNE-20</t>
+          <t>DNE-21</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>2.12 and 2.13 COE</t>
+          <t>3.1 Archetype to Actuals</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Move the netting lines to actual: BP 2.20 becomes 2.3135, DA 1.40 becomes 1.6647.</t>
+          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>DONE: 2.12 netting -2.3135, 2.13 netting -1.3889 (Hold DA at zero), live off the group totals; gate G 4/4.</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr"/>
+          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
       <c r="H71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DNE-21</t>
+          <t>DNE-22</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>3.1 Archetype to Actuals</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>3.1 shows COE cost gross, ignoring the BP and DA netting that 2.12 and 2.13 apply. Make...</t>
+          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.1 COE rows netted 3.8631 / 3.3863; gate G.</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr"/>
+          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>DNE-22</t>
+          <t>DNE-23</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Rechargeable, never to projects. Delete the per FTE and percentage of squad cost metrics.</t>
+          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>DONE: rechargeable language throughout the new content; hygiene gate J 6/6.</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr"/>
+          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>DNE-23</t>
+          <t>DNE-24</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Role ID on every role, every join re-keyed to it. The ID belongs to the role so a vacan...</t>
+          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>DONE: Role ID R0001-R0528 on REVIEW, 2,683 refs re-keyed by ID, zero row-anchored refs left; shuffle test: controls 0, totals identical; gate L 5/5.</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr"/>
+          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>DNE-24</t>
+          <t>DNE-25</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Lock formulas, leave lever dropdowns and cream inputs open, lock structure.</t>
+          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>DONE, then re-scoped on 05/08: protection sits on the 0.x and 3.x tabs only, the role mapping and the lever tabs are open, structure still locked, password Tdd123.</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr"/>
+          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr"/>
       <c r="H75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>DNE-25</t>
+          <t>DNE-26</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Overheads / Head of Tech</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Break proof test: sort the mapping and paste a shuffled extract over it, prove every co...</t>
+          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>DONE: the break-proof test ran and passed, full random shuffle of the mapping, every control 0, every total identical.</t>
-        </is>
-      </c>
-      <c r="G76" s="22" t="inlineStr"/>
+          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DNE-26</t>
+          <t>DNE-27</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Head of Tech</t>
+          <t>Overheads / Tech Manager</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Ed Tacey on or off the Head of Technology line. His title is AI Enablement Lead and he ...</t>
+          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>DONE: Ed Tacey off the Heads line, block row moved to the Leadership group on 2.2; HoT 15 / 4.9089; gate A.</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr"/>
+          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr"/>
       <c r="H77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>DNE-27</t>
+          <t>DNE-28</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Tech Manager</t>
+          <t>Overheads / Business Partner</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Shane Ker in or out of Technology Manager. Not on your list of 24. His title in the dat...</t>
+          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>DONE: Shane Ker stays; TM 25 / 6.7767; gate A.</t>
-        </is>
-      </c>
-      <c r="G78" s="22" t="inlineStr"/>
+          <t>DONE: Neil Reilly in at 666,088.</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>DNE-28</t>
+          <t>DNE-29</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Overheads / Business Partner</t>
+          <t>Overheads / Domain Architect</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Neil Reilly is costed at 666,088, nearly double every other Business Partner and 29% of...</t>
+          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>DONE: Neil Reilly in at 666,088.</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr"/>
+          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr"/>
       <c r="H79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>DNE-29</t>
+          <t>DNE-30</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Overheads / Domain Architect</t>
+          <t>GM layer</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>4 of the 7 Domain Architects are vacant. Decide whether vacant roles are shared across ...</t>
+          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>DONE: vacant-on-Hire priced and shared, Holds at zero everywhere; gate F.</t>
-        </is>
-      </c>
-      <c r="G80" s="22" t="inlineStr"/>
+          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr"/>
       <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DNE-30</t>
+          <t>DNE-31</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>GM layer</t>
+          <t>Single lens</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>How the 8 GMs are priced in: shared equally across the 10 portfolios, or charged to the...</t>
+          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>DONE: GM 5.10 shared 0.510 per portfolio on the Lights On tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr"/>
+          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
       <c r="H81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>DNE-31</t>
+          <t>DNE-32</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Single lens</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber reads 0.805 on 0.2 and 0.838 on 3.1. Pick one basis for the whole book.</t>
+          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>DONE: 0.2 TDD Cyber reads the accurate basis 0.8384; gate H 2/2.</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr"/>
+          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DNE-32</t>
+          <t>DNE-33</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>Overheads / programmes</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Where the actuals lights on view lives: its own tab, a block on each 1.x tab, or both.</t>
+          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>DONE: lights on is its own tab, 3.5 TDD Lights On.</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr"/>
+          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>DNE-33</t>
+          <t>DNE-34</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Overheads / programmes</t>
+          <t>2.1 Ampol Retail</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Whether AmPOS and CTRM carry overhead. You ruled EGI does not.</t>
+          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>DONE: no overhead on EGI, AmPOS, CTRM anywhere in the tab's build; gate F.</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr"/>
+          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>DNE-34</t>
+          <t>DNE-35</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>2.1 Ampol Retail</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Viren Khatri, the single EGI TDD role on Ampol Retail. Retag his squad, move him to TDD...</t>
+          <t>Blank password or a real one.</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>DONE: Viren Khatri on 2.4 EGI TDD, 5 roles / 1.3245; gate C.</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr"/>
+          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>DNE-35</t>
+          <t>DNE-36</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>REVIEW mapping / data</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Blank password or a real one.</t>
+          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>DONE: password Tdd123. The role mapping is no longer locked - your 05/08 ruling opened it.</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr"/>
+          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DNE-36</t>
+          <t>DNE-37</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping / data</t>
+          <t>Lights On tab</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Seven part time people are costed at full rate, not scaled by their FTE.</t>
+          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>DONE: the seven part-time people scaled by FTE, 0.3646 total; gate D 21/21.</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr"/>
+          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DNE-37</t>
+          <t>DNE-38</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Lights On tab</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>New tab, his five columns (Cost, Support Cost, Overhead cost, TDD Lights On budget, Ove...</t>
+          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>DONE: 3.5 TDD Lights On built with his 15 headers verbatim, all live, toggles cream 0-100 in 5s, analysis block live; gate E 20/20 tied at 1e-6. K total 60.93 vs 50.50. Superseded on 05/08 by the eighteen column rebuild.</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr"/>
+          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>DNE-38</t>
+          <t>DNE-39</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>New 30/07 ingest</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Recode the vacant Delivery Assurance Manager and Delivery Excellence Manager onto the D...</t>
+          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>DONE: Delivery Assurance and Delivery Excellence Managers on the DM line, 12 roles; gate A.</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr"/>
+          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>DNE-39</t>
+          <t>DNE-40</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>New 30/07 ingest</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Bring in the lever changes from the new 30/07 workbook he is about to upload, and only ...</t>
+          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>DONE: his 11 lever edits ingested person-keyed (the old-version ledger trap caught and documented); gate B 23/23.</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr"/>
+          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DNE-40</t>
+          <t>DNE-41</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -2924,782 +2916,782 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Price overheads at platform and portfolio level only. Squads carry none. TDD funds ever</t>
+          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>DONE: this IS the Lights On tab's engine, overheads priced at platform and portfolio, squads carry none, nothing recharged; gate E.</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr"/>
+          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>DNE-41</t>
+          <t>DNE-42</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Lights on view</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Share Business Partners and Domain Architects equally across the 10 portfolios at actua</t>
+          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>DONE: BP 0.2314 and DA 0.1389 shares live on the tab; gate E.</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="inlineStr"/>
+          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>DNE-42</t>
+          <t>DNE-43</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Lights on view</t>
+          <t>2.7, 2.8 and 2.10</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Build actuals through the lights on structure: squads at actual with the archetype supp</t>
+          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>DONE: built as 3.5 TDD Lights On with his columns; superseded into BLD-23.</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr"/>
+          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr"/>
       <c r="H93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>DNE-43</t>
+          <t>DNE-44</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>2.7, 2.8 and 2.10</t>
+          <t>1.10 Z Retail</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Four filled people still carry the lever Hire. No cost effect but it is stale state.</t>
+          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>DONE: five, not four - Prem Shetty and Karla Orozco Loza on 2.7, Nico Lender and Hitesh Patel on 2.8, Emma Natoli on 2.10, all set to Filled. Filled and Hire both price at cost factor 1, so nothing moved: 29,683 cached values compared before and after, only the five lever cells differ.</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr"/>
+          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DNE-44</t>
+          <t>DNE-45</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>1.10 Z Retail</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Row 17 pulls a dash from your 0.1 tab. Render it as 0.00 on the model tab.</t>
+          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>DONE: 1.10 I17 wrapped in N(), so the text on your 0.1 tab reads as zero and the cell prints 0.00. Your 0.1 cell is untouched and the Z-Energy budget total still reads 76.60.</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr"/>
+          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DNE-45</t>
+          <t>DNE-46</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Your master role mapping is the file of record - 526 rows, 29 columns, your headers kept verbatim.</t>
+          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>DONE: the raw block replaced cell for cell from your 05/08 file, every 2.x block re-homed off it, levers carried person by person, part-time people priced at FTE on top.</t>
-        </is>
-      </c>
-      <c r="G96" s="22" t="inlineStr"/>
+          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>DNE-46</t>
+          <t>DNE-47</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Overheads / TDD Cyber</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Protection only where nobody types: the 0.x and 3.x tabs. Everything else open, the role mapping included.</t>
+          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>DONE: the 0.x and 3.x tabs carry protection with the password Tdd123 and nothing else does - the role mapping, Lists, the executive summary, every 1.x and 2.x tab and the QA tab are open. Workbook structure stays locked, and the Lights On toggles stay editable behind the protection.</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr"/>
+          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr"/>
       <c r="H97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DNE-47</t>
+          <t>DNE-48</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Overheads / TDD Cyber</t>
+          <t>Language / Enterprise Data</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>TDD Cyber carries an overhead share the same way a portfolio does.</t>
+          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>DONE: the Business Partner, Domain Architect and GM pots divide by eleven - the ten portfolios plus TDD Cyber - on the Lights On tabs.</t>
-        </is>
-      </c>
-      <c r="G98" s="22" t="inlineStr"/>
+          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>DNE-48</t>
+          <t>DNE-49</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Language / Enterprise Data</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>TDD Data is not a thing: the line reads Enterprise Data everywhere, 0.2 included.</t>
+          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>DONE: 0.2's budget line relabelled Enterprise Data and the Lights On rows carry the same label, reading that budget line live.</t>
-        </is>
-      </c>
-      <c r="G99" s="23" t="inlineStr"/>
+          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
+        </is>
+      </c>
+      <c r="G99" s="22" t="inlineStr"/>
       <c r="H99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DNE-49</t>
+          <t>DNE-50</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Customer split into an Ampol Customer and a Z Customer row, with the overheads divided between the two rather than each carrying its own.</t>
+          <t>A duplicate of the Lights On tab split AU against NZ.</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>DONE: both rows on the tab; the shares and the Customer overhead pool split between them in proportion to their support cost.</t>
-        </is>
-      </c>
-      <c r="G100" s="22" t="inlineStr"/>
+          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>DNE-50</t>
+          <t>DNE-51</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>A duplicate of the Lights On tab split AU against NZ.</t>
+          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>DONE: 3.6 TDD Lights On AU NZ - the same rows with AU spend, NZ spend, total and variance against your 0.2 AU and NZ budgets, and the split basis stated on the tab in plain English.</t>
-        </is>
-      </c>
-      <c r="G101" s="23" t="inlineStr"/>
+          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr"/>
       <c r="H101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>DNE-51</t>
+          <t>DNE-52</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>COE pair rows</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Rebuilt on his eighteen columns, every cost represented once.</t>
+          <t>Each COE line carries its own people, not a proportional share.</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>DONE: his eighteen headings verbatim, rows are the 0.2 Data Config set. Total People cost 105.28 = 104.78 after levers + 0.49 cyber uplift charge. Charged to TDD 61.04 against 50.50 allocated (over 10.54) and the 53.80 budget (over 7.24). Support 37.87, overheads charged 23.17, noted in 1.x 34.38. Toggles cream on the fifteen rows that scale something.</t>
-        </is>
-      </c>
-      <c r="G102" s="22" t="inlineStr"/>
+          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>DNE-52</t>
+          <t>DNE-53</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>COE pair rows</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Each COE line carries its own people, not a proportional share.</t>
+          <t>EGI is EGI - the whole family in one place.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>DONE: squad truth per column - Strategy Architecture 3.34, Transformation 2.88, Business Partnering 3.29, Data 1.43; each line prices its charge off its planned spend line and notes the pot it holds (BP 2.31, DA 1.39), so Still left to fund reads 0 on every COE line - the pots are funded inside the eleven allocation columns, nothing is double shown.</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr"/>
+          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
+        </is>
+      </c>
+      <c r="G103" s="22" t="inlineStr"/>
       <c r="H103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>DNE-53</t>
+          <t>DNE-54</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>EGI is EGI - the whole family in one place.</t>
+          <t>The tab must read exactly as his file does, visibility included.</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>DONE: six squads, 41 roles, 10.24 on 2.14; the portfolio tabs' EGI rows read 0; 3.4 lists the six squads live off the role mapping; no EGI cost in support, the shares or the overheads.</t>
-        </is>
-      </c>
-      <c r="G104" s="22" t="inlineStr"/>
+          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>DNE-54</t>
+          <t>DNE-55</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>REVIEW mapping</t>
+          <t>3.5 TDD Lights On</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>The tab must read exactly as his file does, visibility included.</t>
+          <t>Show how the columns add to the total people cost.</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>DONE: 513 hidden rows inherited from the old lock unhidden - his 05/08 file hides none. The gate now checks visibility against his file permanently.</t>
-        </is>
-      </c>
-      <c r="G105" s="23" t="inlineStr"/>
+          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
+        </is>
+      </c>
+      <c r="G105" s="22" t="inlineStr"/>
       <c r="H105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>DNE-55</t>
+          <t>DNE-56</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>3.5 TDD Lights On</t>
+          <t>EGI</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>Show how the columns add to the total people cost.</t>
+          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr"/>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>DONE: a live block under the table. 105.28 less 19.07 funded outside equals 86.21 for TDD to fund; less 59.39 charged to lights on equals 26.82 to recharge; less 34.38 noted in the 1.x tabs equals (7.57) still to fund. A second block splits the 59.39: support 36.22, BP 2.31, DA 1.39, GM 5.10, other overheads after the toggles 14.37, against the 53.80 budget, 5.59 over.</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="inlineStr"/>
+          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>DNE-56</t>
+          <t>DNE-57</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>EGI</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>EGI cost shows in the portfolio that has it and nets out in Sig items funded.</t>
+          <t>The GM cost splits across the COEs as well as the portfolios.</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>DONE: EGI is keyed on your Platform column, 49 roles / 12.07. The EGI squads sit in the portfolio they name, the EGI Ent Data row is built on 2.3 from your own 1.3 label, and every portfolio shows its EGI cost in Total people cost and nets it out in Sig items funded. Only the plain EGI squad, 18 roles / 5.15, stays on the EGI row.</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="inlineStr"/>
+          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="inlineStr"/>
       <c r="H107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>DNE-57</t>
+          <t>DNE-58</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>The GM cost splits across the COEs as well as the portfolios.</t>
+          <t>Get rid of the control checks.</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr"/>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>DONE: the GM pot divides over sixteen, the eleven portfolio units plus the five COE lines, 0.32 each. Business Partner and Domain Architect stay over eleven.</t>
-        </is>
-      </c>
-      <c r="G108" s="22" t="inlineStr"/>
+          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>DNE-58</t>
+          <t>DNE-59</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>0.2 Data Config</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Get rid of the control checks.</t>
+          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>DONE: 56 control rows and the 4.0 Data QA tab removed. Every reconciliation they proved is now checked outside the workbook by the gate, which runs 189 checks.</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="inlineStr"/>
+          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr"/>
       <c r="H109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>DNE-59</t>
+          <t>DNE-60</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>0.2 Data Config</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>0.2 and 3.5 must not price the same portfolio differently.</t>
+          <t>One sign convention for over budget.</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr"/>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>DONE: they disagreed by 4.43 across 12 of 18 rows, five flipping sign, because 0.2 priced support at the archetype rate and 3.5 at actual after levers. 0.2 now reads 3.5 row for row.</t>
-        </is>
-      </c>
-      <c r="G110" s="22" t="inlineStr"/>
+          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>DNE-60</t>
+          <t>DNE-61</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>1.x tabs</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>One sign convention for over budget.</t>
+          <t>The eleven 1.x tabs made genuinely like for like.</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>DONE: over budget reads positive everywhere. It was negative on 0.2 and the 2.x funding blocks and positive on 3.5, 3.6 and the 1.x tabs, and since every tab brackets negatives a bracket meant good on one tab and bad on another.</t>
-        </is>
-      </c>
-      <c r="G111" s="23" t="inlineStr"/>
+          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
+        </is>
+      </c>
+      <c r="G111" s="22" t="inlineStr"/>
       <c r="H111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>DNE-61</t>
+          <t>DNE-62</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>1.x tabs</t>
+          <t>3.6 TDD Lights On AU NZ</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>The eleven 1.x tabs made genuinely like for like.</t>
+          <t>Answer whether the overspend is AU or NZ.</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr"/>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>DONE: 1.7's block aligned with its ten siblings (and a formula that read the NZ budget where its siblings read the NZ variance, corrected), 1.5 given the NZ column its budget needs, the budget and funding blocks on one shape, one label over the block and one on the total.</t>
-        </is>
-      </c>
-      <c r="G112" s="22" t="inlineStr"/>
+          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
+        </is>
+      </c>
+      <c r="G112" s="23" t="inlineStr"/>
       <c r="H112" s="15" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>DNE-62</t>
+          <t>DNE-63</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>3.6 TDD Lights On AU NZ</t>
+          <t>FY26 forecast</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Answer whether the overspend is AU or NZ.</t>
+          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr"/>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>DONE: AU 44.96 against 33.00 is 11.96 over; NZ 16.08 against 17.50 is 1.42 under. The duplicated variance column is gone.</t>
-        </is>
-      </c>
-      <c r="G113" s="23" t="inlineStr"/>
+          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
+        </is>
+      </c>
+      <c r="G113" s="22" t="inlineStr"/>
       <c r="H113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>DNE-63</t>
+          <t>DNE-64</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>One workbook: Finance actuals to June plus the model's remaining months, charged vs recharged, AU and NZ, vacancy hire months.</t>
+          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr"/>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>DONE: TDD_FY26_Forecast.xlsx shipped 06/08. Landing 56.68 charged, 6.18 over the 50.50 allocations, 2.88 over the 53.80 budget; AU 39.75 over by 3.55, NZ 16.93 under by 0.67. Six actual months at people scope from Finance's file, six modelled at the model's run rate; 70 vacancy hire-month dropdowns default to full months; Finance's own outlook 54.30 shown beside it. Open: Lee's hire months, mapping confirms on 0.3, July actuals when they exist.</t>
-        </is>
-      </c>
-      <c r="G114" s="22" t="inlineStr"/>
+          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr"/>
       <c r="H114" s="15" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>DNE-64</t>
+          <t>DNE-65</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>FY26 forecast v3</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Finance's cut from the June TDD Pack, closed actuals, their monthly forecast, budgets 36.2/17.6 from 0.2 row 27, AUD lights-on block, two-Junes and 0.92 findings baked in.</t>
+          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr"/>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>Shipped 09/08 within Lee's one-hour cap: analysis, Opus build agent (stopped correctly on the two-Junes conflict), ruling, rebuild, double verification, QA render.</t>
-        </is>
-      </c>
-      <c r="G115" s="23" t="inlineStr"/>
+          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
+        </is>
+      </c>
+      <c r="G115" s="22" t="inlineStr"/>
       <c r="H115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>DNE-65</t>
+          <t>DNE-66</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3</t>
+          <t>Exec deck v1</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>Live FX input, 50.5 anchor, model-driven H2 less vacancy timing relief, 107-row hire-month tab, sources tab naming every refresh point.</t>
+          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
         </is>
       </c>
       <c r="E116" s="19" t="inlineStr"/>
       <c r="F116" s="14" t="inlineStr">
         <is>
-          <t>Shipped 09/08. Landing 52.42 vs 50.5 at 0.83 FX. QA: checks Yes, 2 cream cells, 0 italics, 0 external links.</t>
-        </is>
-      </c>
-      <c r="G116" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
+        </is>
+      </c>
+      <c r="G116" s="23" t="inlineStr"/>
       <c r="H116" s="15" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>DNE-66</t>
+          <t>DNE-67</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Exec deck v1</t>
+          <t>FY26 forecast v3.1</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>15 slides, template identity, 10 native charts, Minto storyline, FY26 slide on the v3 live-FX basis, 2 option slides.</t>
+          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
         </is>
       </c>
       <c r="E117" s="18" t="inlineStr"/>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after QA fixes (cyber split rows, spans data, FY26 restatement).</t>
-        </is>
-      </c>
-      <c r="G117" s="23" t="inlineStr"/>
+          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
+        </is>
+      </c>
+      <c r="G117" s="22" t="inlineStr"/>
       <c r="H117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>DNE-67</t>
+          <t>DNE-68</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v3.1</t>
+          <t>Deck v2 pass one</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>Updated-model refresh (54.12 basis, revert-ready), NZ takes its own timing relief, monthly view tab with actual/forecast split, banned-word sweep.</t>
+          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
         </is>
       </c>
       <c r="E118" s="19" t="inlineStr"/>
       <c r="F118" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08. Total landing 52.45 vs 50.5 at 0.83 FX.</t>
-        </is>
-      </c>
-      <c r="G118" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 after independent QA.</t>
+        </is>
+      </c>
+      <c r="G118" s="23" t="inlineStr"/>
       <c r="H118" s="15" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>DNE-68</t>
+          <t>DNE-69</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 pass one</t>
+          <t>Deck v2 final</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>17 slides inside Lee's own file, 8 native charts, mekko+dumbbells drawn, MBB anatomy, cull list numbered. Pass two adds insight slides from the miner.</t>
+          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
         </is>
       </c>
       <c r="E119" s="18" t="inlineStr"/>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after independent QA.</t>
-        </is>
-      </c>
-      <c r="G119" s="23" t="inlineStr"/>
+          <t>Shipped 10/08 after redirect + QA.</t>
+        </is>
+      </c>
+      <c r="G119" s="22" t="inlineStr"/>
       <c r="H119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>DNE-69</t>
+          <t>DNE-70</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>Deck v2 final</t>
+          <t>Wave Q package</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>22 slides / 17 content / 14 native charts in Lee's file, his spec only, banned-word sweep incl floor, budget answer locked (FY26 inside full budget; FY27 48.50 with two decisions).</t>
+          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
         </is>
       </c>
       <c r="E120" s="19" t="inlineStr"/>
       <c r="F120" s="14" t="inlineStr">
         <is>
-          <t>Shipped 10/08 after redirect + QA.</t>
-        </is>
-      </c>
-      <c r="G120" s="22" t="inlineStr"/>
+          <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
+        </is>
+      </c>
+      <c r="G120" s="23" t="inlineStr"/>
       <c r="H120" s="15" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>DNE-70</t>
+          <t>DNE-71</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Wave Q package</t>
+          <t>FY27 dashboard rebuild</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Deck v2 final (22 slides, exec summary up front, all sweeps zero) + TDD_FY26_Forecast v4 (landing 53.72, ten checks). The FY26 relief-basis defect found and fixed in the loop.</t>
+          <t>Rebuilt 28/08 on the new model per the option pack rulings: overheads KPI band and typed line on all 13 portfolio tabs, platform grouped squad chart, platform cost chart and FTE chart, Squad cost block, Lever mix and Cost per FTE tabs added after Squads. Corporate and every carried tab identical to the previous ship.</t>
         </is>
       </c>
       <c r="E121" s="18" t="inlineStr"/>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>Shipped 10/08 pm after three agent rounds and two QA gates.</t>
-        </is>
-      </c>
-      <c r="G121" s="23" t="inlineStr"/>
+          <t>SHIPPED 28/08: recalc three inherited #N/A only, checker zero findings, 15 tabs rendered and read; anchors 98.98 / 54.20 / 50.5 (3.70 over) / 53.8 (0.40 over) / 537.8 all tie.</t>
+        </is>
+      </c>
+      <c r="G121" s="22" t="inlineStr"/>
       <c r="H121" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>31 decisions, 12 to build, 70 done.</t>
+          <t>31 decisions, 11 to build, 71 done.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B123:H123"/>
+    <mergeCell ref="B50:H50"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B51:H51"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="G6:G122" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -3672,7 +3672,7 @@
       <c r="E121" s="18" t="inlineStr"/>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>SHIPPED 28/08: recalc three inherited #N/A only, checker zero findings, 15 tabs rendered and read; anchors 98.98 / 54.20 / 50.5 (3.70 over) / 53.8 (0.40 over) / 537.8 all tie.</t>
+          <t>SHIPPED 28/08, re-shipped same day: Excel refused the first file. Root cause: the recalculation step saves the workbook through LibreOffice, which rewrote the grouped chart's two-column axis into a form Excel rejects. Grouped chart rebuilt as one coloured series per platform on a single squad axis; a permanent Excel-openability gate now checks every build against the last file that opened. All gates green: recalc three inherited #N/A only, checker zero findings, anchors 98.98 / 54.20 / 50.5 / 53.8 / 537.8 tie.</t>
         </is>
       </c>
       <c r="G121" s="22" t="inlineStr"/>

--- a/docs/TDD_Model_Register.xlsx
+++ b/docs/TDD_Model_Register.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H123"/>
+  <dimension ref="B2:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NEEDS YOUR DECISION  (31)</t>
+          <t>NEEDS YOUR DECISION  (34)</t>
         </is>
       </c>
     </row>
@@ -1579,103 +1579,103 @@
       <c r="H37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>AGREED, NOT BUILT YET  (11)</t>
-        </is>
-      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>DEC-43</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio cost bases</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise platforms, one decision for both: the Microsoft estate (24,474,946.34 gross, 19,337,946.48 net of the Z recovery) sits in TDD Group Functions and SAP ERP (5,344,596.73) sits in Finance because those lines pay the vendor. Pool and allocate them across portfolios, or leave them with the paying line?</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Live rows on the workbook's Non-labour detail tab; the same logic must answer both.</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BLD-11</t>
+          <t>DEC-44</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Portfolio cost bases</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Single lens everywhere so no number needs interpreting.</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr"/>
+          <t>Two splits offered from your own budget tab, not applied: cyber cost centre HITSEC 69.1% TDD Cyber (4,111,767.81) / 30.9% COE Cyber (1,838,692.12); Data Analytics and AI 40.2% Enterprise Data (409,619.62) / 59.8% COE SA&amp;D (608,878.16). Apply, or leave held?</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Ratios are your budget tab's own; one word applies them.</t>
+        </is>
+      </c>
       <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
-        </is>
-      </c>
+      <c r="H39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>BLD-15</t>
+          <t>DEC-45</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Whole model</t>
+          <t>Portfolio cost bases</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr"/>
+          <t>Depreciation 5,813,179.65 sits inside the FY26 actuals base while capex is ruled out for now; and 800254 contractors 26,080,471.99 are ruled non-labour on your own hierarchy pending how the labour model defines them. Confirm both treatments.</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Both stated on the face and in the findings, nothing plugged.</t>
+        </is>
+      </c>
       <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="15" t="inlineStr">
-        <is>
-          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
-        </is>
-      </c>
+      <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>BLD-20</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>COE tabs</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>AGREED, NOT BUILT YET  (11)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>BLD-21</t>
+          <t>BLD-11</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Give the full list of everything changed or removed that you never asked for.</t>
+          <t>Single lens everywhere so no number needs interpreting.</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1697,103 +1697,111 @@
       <c r="G42" s="9" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>what have you changed that i didn't ask for?</t>
+          <t>I need this to be a perfect model that requires no analysis or interpretation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BLD-12</t>
+          <t>BLD-15</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
-        </is>
-      </c>
+          <t>Like for like tabs made consistent in formatting, language, layout and design.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Ensure that like for like tabs have consistent formatting, language, layout, design etc.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BLD-13</t>
+          <t>BLD-20</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>0.0 Cockpit</t>
+          <t>COE tabs</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Deliver the one page explanation of why one COE tab not two, and why the old numbers contradicted. You approved the consolidation but never got the explanation.</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="15" t="inlineStr"/>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>i also expect absolute clarity as to why we would have 1 tab vs 2 and why the numbers and explanations are contradictory</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>BLD-14</t>
+          <t>BLD-21</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>All 2.x tabs</t>
+          <t>Whole model</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>Give the full list of everything changed or removed that you never asked for.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr"/>
       <c r="G45" s="9" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>what have you changed that i didn't ask for?</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>BLD-22</t>
+          <t>BLD-12</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2.9 Commercial Fuels</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+          <t>FY27 landing view with three date assumptions and an FY27 column on the role blocks.</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -1803,7 +1811,7 @@
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Mechanically right, reads odd.</t>
+          <t>Verified absent as a view. FY27 appears only as a side note on 3 tabs.</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr"/>
@@ -1812,226 +1820,230 @@
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>BLD-23</t>
+          <t>BLD-13</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>0.0 Cockpit</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
-        </is>
-      </c>
+          <t>New cockpit tab: headline tiles, budget against spend, funded outside legend, levers live today, FY27.</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr"/>
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>BLD-24</t>
+          <t>BLD-14</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>FY26 forecast v2</t>
+          <t>All 2.x tabs</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>Done - replaced by the Finance-cut build.</t>
-        </is>
-      </c>
+          <t>Cockpit strip on every 2.x tab, in cell bars, consistent formats.</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>BLD-25</t>
+          <t>BLD-22</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Wave Q exec deck</t>
+          <t>2.9 Commercial Fuels</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>DONE</t>
+          <t>CTRM is funded at a flat 3.800 while its roles cost 3.2218, so TDD funded reads (0.578). Decide whether to show it that way or net it.</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Delivered with the compliance summary and cull list.</t>
+          <t>Mechanically right, reads odd.</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (71)</t>
-        </is>
-      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>BLD-23</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>1.2 Customer</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Digital Support NZ is an archetype-only squad (100% support, 0.32 planned, no roles), so no 2.2 grid row exists for its Support % to move to in the wiring move. It stays typed on 1.2 G41 for now.</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Needs a ruling: keep on 1.2, or add a 2.2 row when it gets roles.</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DNE-01</t>
+          <t>BLD-24</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2.3 Enterprise Data</t>
+          <t>FY26 forecast v2</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="inlineStr"/>
+          <t>Superseded by Lee's 09/08 ruling: built on Finance's cut instead (see DEC-28). v2 shipped from the June file with 0.2 row-27 budgets.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr"/>
+          <t>Done - replaced by the Finance-cut build.</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DNE-02</t>
+          <t>BLD-25</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2.x lever tabs</t>
+          <t>Wave Q exec deck</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
-        </is>
-      </c>
-      <c r="E52" s="19" t="inlineStr"/>
+          <t>SHIPPED 10/08 pm: deck 22 slides / 14 native charts, formatting normalised to slides 2-4, story order, 16-fix round + full-transcript instruction audit (107 instructions, six gaps closed); FY26 workbook v4 on the corrected what-TDD-pays basis, ten checks pass. Deck and workbook reconcile to the cent.</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>67 levers live, 8.17m impact</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr"/>
+          <t>Delivered with the compliance summary and cull list.</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>DNE-03</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>REVIEW mapping</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr"/>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr"/>
-      <c r="H53" s="10" t="inlineStr"/>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>DONE AND VERIFIED IN THE SHIPPED FILE  (72)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>DNE-04</t>
+          <t>DNE-01</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>0.1 and 1.2</t>
+          <t>2.3 Enterprise Data</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
+          <t>The 8 EGI roles funded by EGI on their own directly funded line</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr"/>
+          <t>Verified: 2.3 EGI line, 8 roles, 1.8119</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DNE-05</t>
+          <t>DNE-02</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>2.x lever tabs</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Programme Management as a Customer only overhead line</t>
+          <t>All Hold hacks reversed, your 8.98m of lever plays left live</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>3 roles, 0.7612, allocated at its own cost</t>
-        </is>
-      </c>
-      <c r="G55" s="22" t="inlineStr"/>
+          <t>67 levers live, 8.17m impact</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DNE-06</t>
+          <t>DNE-03</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -2041,32 +2053,32 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Ed Tacey follows the data onto the Heads line</t>
+          <t>Named vacancies filled, three Remove rows deleted, Nico Lender fills one role</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>Verified row 161. Now under review, see DEC-02</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr"/>
+          <t>Superseded by your 05/08 master mapping, which is now the file of record.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DNE-07</t>
+          <t>DNE-04</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1.2 Customer</t>
+          <t>0.1 and 1.2</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
+          <t>Significant Items budget 4.5, 1.2 relinked not hardcoded</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
@@ -2075,163 +2087,163 @@
           <t>Verified</t>
         </is>
       </c>
-      <c r="G57" s="22" t="inlineStr"/>
+      <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>DNE-08</t>
+          <t>DNE-05</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Contractor end dates parked, four Move to Z Customer people parked</t>
+          <t>Programme Management as a Customer only overhead line</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr"/>
+          <t>3 roles, 0.7612, allocated at its own cost</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DNE-09</t>
+          <t>DNE-06</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>REVIEW mapping</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>13/07 EGI portfolio moves not adopted, only its role mapping tab used</t>
+          <t>Ed Tacey follows the data onto the Heads line</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G59" s="22" t="inlineStr"/>
+          <t>Verified row 161. Now under review, see DEC-02</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>DNE-10</t>
+          <t>DNE-07</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>COE tabs</t>
+          <t>1.2 Customer</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>COEs consolidated to one 2.x tab each, funding blocks moved onto them</t>
+          <t>Digital Support NZ at archetype 0.32 with your 0.217 called out on tab</t>
         </is>
       </c>
       <c r="E60" s="19" t="inl